--- a/data/obx_xlsx/NKR.OL.xlsx
+++ b/data/obx_xlsx/NKR.OL.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="485">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -907,6 +907,9 @@
   </si>
   <si>
     <t>Total other non-current liabilities</t>
+  </si>
+  <si>
+    <t>Convertible Callable Unsecured Subordinated Bond (Do not use)</t>
   </si>
   <si>
     <t>Liabilities to Credit Institutions</t>
@@ -1596,7 +1599,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1674,6 +1677,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -14652,8 +14658,8 @@
       <c r="W140" s="15"/>
     </row>
     <row r="141" ht="15.0" customHeight="1">
-      <c r="A141" s="13" t="s">
-        <v>270</v>
+      <c r="A141" s="26" t="s">
+        <v>296</v>
       </c>
       <c r="B141" s="15"/>
       <c r="C141" s="15"/>
@@ -14692,7 +14698,7 @@
     </row>
     <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B142" s="15"/>
       <c r="C142" s="15"/>
@@ -14731,7 +14737,7 @@
     </row>
     <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="13" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B143" s="15"/>
       <c r="C143" s="15"/>
@@ -14762,7 +14768,7 @@
     </row>
     <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B144" s="15"/>
       <c r="C144" s="15"/>
@@ -14791,7 +14797,7 @@
     </row>
     <row r="145" ht="15.0" customHeight="1">
       <c r="A145" s="13" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B145" s="15"/>
       <c r="C145" s="15"/>
@@ -14824,7 +14830,7 @@
     </row>
     <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B146" s="23">
         <v>0.0</v>
@@ -14857,7 +14863,7 @@
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="17" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B147" s="20">
         <v>86.06</v>
@@ -14928,7 +14934,7 @@
     </row>
     <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B148" s="15"/>
       <c r="C148" s="15"/>
@@ -14961,7 +14967,7 @@
     </row>
     <row r="149" ht="15.0" customHeight="1">
       <c r="A149" s="17" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B149" s="18">
         <v>375.47</v>
@@ -15032,7 +15038,7 @@
     </row>
     <row r="150" ht="15.0" customHeight="1">
       <c r="A150" s="13" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B150" s="16">
         <v>11.82</v>
@@ -15103,7 +15109,7 @@
     </row>
     <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B151" s="21">
         <v>-1.02</v>
@@ -15172,7 +15178,7 @@
     </row>
     <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="13" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B152" s="16">
         <v>9.21</v>
@@ -15241,7 +15247,7 @@
     </row>
     <row r="153" ht="15.0" customHeight="1">
       <c r="A153" s="13" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B153" s="14">
         <v>276.02</v>
@@ -15312,7 +15318,7 @@
     </row>
     <row r="154" ht="15.0" customHeight="1">
       <c r="A154" s="13" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B154" s="15"/>
       <c r="C154" s="15"/>
@@ -15341,7 +15347,7 @@
     </row>
     <row r="155" ht="15.0" customHeight="1">
       <c r="A155" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B155" s="15"/>
       <c r="C155" s="15">
@@ -15382,7 +15388,7 @@
     </row>
     <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="17" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B156" s="18">
         <v>296.02</v>
@@ -15453,7 +15459,7 @@
     </row>
     <row r="157" ht="15.0" customHeight="1">
       <c r="A157" s="13" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B157" s="16">
         <v>71.77</v>
@@ -15502,7 +15508,7 @@
     </row>
     <row r="158" ht="15.0" customHeight="1">
       <c r="A158" s="13" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B158" s="15"/>
       <c r="C158" s="23">
@@ -15533,7 +15539,7 @@
     </row>
     <row r="159" ht="15.0" customHeight="1">
       <c r="A159" s="17" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B159" s="20">
         <v>71.77</v>
@@ -15582,7 +15588,7 @@
     </row>
     <row r="160" ht="15.0" customHeight="1">
       <c r="A160" s="17" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B160" s="18">
         <v>367.79</v>
@@ -15653,7 +15659,7 @@
     </row>
     <row r="161" ht="15.0" customHeight="1">
       <c r="A161" s="13" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B161" s="15"/>
       <c r="C161" s="15"/>
@@ -15684,7 +15690,7 @@
     </row>
     <row r="162" ht="15.0" customHeight="1">
       <c r="A162" s="17" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B162" s="18">
         <v>743.26</v>
@@ -15755,7 +15761,7 @@
     </row>
     <row r="163" ht="15.0" customHeight="1">
       <c r="A163" s="13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B163" s="14">
         <v>107.43</v>
@@ -15826,7 +15832,7 @@
     </row>
     <row r="164" ht="15.0" customHeight="1">
       <c r="A164" s="13" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B164" s="16">
         <v>9.28</v>
@@ -15897,7 +15903,7 @@
     </row>
     <row r="165" ht="15.0" customHeight="1">
       <c r="A165" s="13" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B165" s="16">
         <v>98.14</v>
@@ -15968,7 +15974,7 @@
     </row>
     <row r="166" ht="15.0" customHeight="1">
       <c r="A166" s="13" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B166" s="15"/>
       <c r="C166" s="15"/>
@@ -15999,7 +16005,7 @@
     </row>
     <row r="167" ht="15.0" customHeight="1">
       <c r="A167" s="13" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B167" s="15"/>
       <c r="C167" s="15"/>
@@ -16032,7 +16038,7 @@
     </row>
     <row r="168" ht="15.0" customHeight="1">
       <c r="A168" s="13" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B168" s="15"/>
       <c r="C168" s="14">
@@ -16061,7 +16067,7 @@
     </row>
     <row r="169" ht="15.0" customHeight="1">
       <c r="A169" s="13" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B169" s="15"/>
       <c r="C169" s="15"/>
@@ -16104,7 +16110,7 @@
     </row>
     <row r="170" ht="15.0" customHeight="1">
       <c r="A170" s="13" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B170" s="15"/>
       <c r="C170" s="15"/>
@@ -16133,7 +16139,7 @@
     </row>
     <row r="171" ht="15.0" customHeight="1">
       <c r="A171" s="13" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B171" s="15"/>
       <c r="C171" s="15"/>
@@ -16164,7 +16170,7 @@
     </row>
     <row r="172" ht="15.0" customHeight="1">
       <c r="A172" s="13" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B172" s="15"/>
       <c r="C172" s="15"/>
@@ -16195,7 +16201,7 @@
     </row>
     <row r="173" ht="15.0" customHeight="1">
       <c r="A173" s="13" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B173" s="15"/>
       <c r="C173" s="15"/>
@@ -16234,7 +16240,7 @@
     </row>
     <row r="174" ht="15.0" customHeight="1">
       <c r="A174" s="13" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B174" s="15"/>
       <c r="C174" s="15"/>
@@ -16275,7 +16281,7 @@
     </row>
     <row r="175" ht="15.0" customHeight="1">
       <c r="A175" s="13" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B175" s="15"/>
       <c r="C175" s="15"/>
@@ -16316,7 +16322,7 @@
     </row>
     <row r="176" ht="15.0" customHeight="1">
       <c r="A176" s="13" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B176" s="15"/>
       <c r="C176" s="15"/>
@@ -16345,7 +16351,7 @@
     </row>
     <row r="177" ht="15.0" customHeight="1">
       <c r="A177" s="13" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B177" s="15"/>
       <c r="C177" s="15"/>
@@ -16378,7 +16384,7 @@
     </row>
     <row r="178" ht="15.0" customHeight="1">
       <c r="A178" s="13" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B178" s="15"/>
       <c r="C178" s="15"/>
@@ -16411,7 +16417,7 @@
     </row>
     <row r="179" ht="15.0" customHeight="1">
       <c r="A179" s="13" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B179" s="15"/>
       <c r="C179" s="15"/>
@@ -16442,7 +16448,7 @@
     </row>
     <row r="180" ht="15.0" customHeight="1">
       <c r="A180" s="13" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B180" s="15"/>
       <c r="C180" s="15"/>
@@ -16473,7 +16479,7 @@
     </row>
     <row r="181" ht="15.0" customHeight="1">
       <c r="A181" s="13" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B181" s="15"/>
       <c r="C181" s="15"/>
@@ -16504,7 +16510,7 @@
     </row>
     <row r="182" ht="15.0" customHeight="1">
       <c r="A182" s="13" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B182" s="15"/>
       <c r="C182" s="15"/>
@@ -16537,7 +16543,7 @@
     </row>
     <row r="183" ht="15.0" customHeight="1">
       <c r="A183" s="13" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B183" s="15"/>
       <c r="C183" s="15"/>
@@ -16570,7 +16576,7 @@
     </row>
     <row r="184" ht="15.0" customHeight="1">
       <c r="A184" s="13" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B184" s="16">
         <v>1.0</v>
@@ -16641,7 +16647,7 @@
     </row>
     <row r="185" ht="15.0" customHeight="1">
       <c r="A185" s="13" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B185" s="14">
         <v>107.43</v>
@@ -16712,7 +16718,7 @@
     </row>
     <row r="186" ht="15.0" customHeight="1">
       <c r="A186" s="13" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B186" s="16">
         <v>9.28</v>
@@ -16783,7 +16789,7 @@
     </row>
     <row r="187" ht="15.0" customHeight="1">
       <c r="A187" s="13" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B187" s="16">
         <v>98.14</v>
@@ -17686,7 +17692,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -18072,75 +18078,75 @@
         <v>44</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -18238,7 +18244,7 @@
     </row>
     <row r="19" ht="15.0" customHeight="1">
       <c r="A19" s="13" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B19" s="21">
         <v>-37.4</v>
@@ -18307,7 +18313,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="13" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B20" s="15"/>
       <c r="C20" s="15"/>
@@ -18336,7 +18342,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="13" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B21" s="15"/>
       <c r="C21" s="15"/>
@@ -18367,7 +18373,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="13" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B22" s="16">
         <v>32.21</v>
@@ -18412,7 +18418,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="13" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -18443,7 +18449,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="13" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
@@ -18494,7 +18500,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="13" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B25" s="15"/>
       <c r="C25" s="16">
@@ -18527,7 +18533,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="13" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B26" s="15"/>
       <c r="C26" s="21">
@@ -18592,7 +18598,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="13" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B27" s="15"/>
       <c r="C27" s="16">
@@ -18645,7 +18651,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="13" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B28" s="15"/>
       <c r="C28" s="21">
@@ -18678,7 +18684,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="13" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B29" s="16">
         <v>25.35</v>
@@ -18737,7 +18743,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="13" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B30" s="21">
         <v>-4.94</v>
@@ -18806,7 +18812,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="13" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -18839,7 +18845,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="13" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
@@ -18870,7 +18876,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="13" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
@@ -18901,7 +18907,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="13" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -18946,7 +18952,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="13" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -19038,7 +19044,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="13" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
@@ -19079,7 +19085,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="13" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
@@ -19128,7 +19134,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="13" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B39" s="15"/>
       <c r="C39" s="15"/>
@@ -19204,7 +19210,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="13" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B41" s="16">
         <v>37.68</v>
@@ -19249,7 +19255,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="13" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
@@ -19327,7 +19333,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="13" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B44" s="16">
         <v>23.82</v>
@@ -19356,7 +19362,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="13" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B45" s="21">
         <v>-69.49</v>
@@ -19397,7 +19403,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="13" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
@@ -19426,7 +19432,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="13" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B47" s="15"/>
       <c r="C47" s="15"/>
@@ -19463,7 +19469,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="13" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
@@ -19496,7 +19502,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="13" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B49" s="15"/>
       <c r="C49" s="15"/>
@@ -19527,7 +19533,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="13" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B50" s="15"/>
       <c r="C50" s="15"/>
@@ -19560,7 +19566,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="13" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B51" s="15"/>
       <c r="C51" s="15"/>
@@ -19593,7 +19599,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="13" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B52" s="15"/>
       <c r="C52" s="15"/>
@@ -19626,7 +19632,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="13" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B53" s="15"/>
       <c r="C53" s="15"/>
@@ -19673,7 +19679,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="17" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B54" s="20">
         <v>35.59</v>
@@ -19744,7 +19750,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="13" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
@@ -19785,7 +19791,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="13" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B56" s="21">
         <v>-19.21</v>
@@ -19832,7 +19838,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="13" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B57" s="15"/>
       <c r="C57" s="15"/>
@@ -19865,7 +19871,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="13" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B58" s="15"/>
       <c r="C58" s="15"/>
@@ -19914,7 +19920,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="13" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B59" s="15"/>
       <c r="C59" s="15"/>
@@ -19949,7 +19955,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="13" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B60" s="15"/>
       <c r="C60" s="15"/>
@@ -19988,7 +19994,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="13" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B61" s="15"/>
       <c r="C61" s="15"/>
@@ -20019,7 +20025,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="13" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B62" s="15"/>
       <c r="C62" s="15"/>
@@ -20056,7 +20062,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="13" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B63" s="15"/>
       <c r="C63" s="15"/>
@@ -20101,7 +20107,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="13" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B64" s="15"/>
       <c r="C64" s="15"/>
@@ -20132,7 +20138,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="13" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B65" s="15"/>
       <c r="C65" s="15"/>
@@ -20179,7 +20185,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="13" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B66" s="15"/>
       <c r="C66" s="15"/>
@@ -20216,7 +20222,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="13" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B67" s="15"/>
       <c r="C67" s="15"/>
@@ -20255,7 +20261,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="13" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B68" s="15"/>
       <c r="C68" s="15"/>
@@ -20292,7 +20298,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="13" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B69" s="15"/>
       <c r="C69" s="15"/>
@@ -20329,7 +20335,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="13" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B70" s="15"/>
       <c r="C70" s="15"/>
@@ -20360,7 +20366,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="13" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B71" s="15">
         <v>0.0</v>
@@ -20395,7 +20401,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="13" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B72" s="15"/>
       <c r="C72" s="15"/>
@@ -20430,7 +20436,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="17" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B73" s="24">
         <v>-19.21</v>
@@ -20501,7 +20507,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="13" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B74" s="15"/>
       <c r="C74" s="15"/>
@@ -20534,7 +20540,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="13" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B75" s="15"/>
       <c r="C75" s="15"/>
@@ -20563,7 +20569,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="13" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B76" s="15"/>
       <c r="C76" s="15"/>
@@ -20610,7 +20616,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="13" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B77" s="15"/>
       <c r="C77" s="15"/>
@@ -20665,7 +20671,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="13" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B78" s="21">
         <v>-64.27</v>
@@ -20700,7 +20706,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="13" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B79" s="15"/>
       <c r="C79" s="15"/>
@@ -20731,7 +20737,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="13" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B80" s="16">
         <v>4.95</v>
@@ -20762,7 +20768,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="13" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B81" s="15"/>
       <c r="C81" s="15"/>
@@ -20817,7 +20823,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="13" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B82" s="15"/>
       <c r="C82" s="15"/>
@@ -20860,7 +20866,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="13" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B83" s="21">
         <v>-6.06</v>
@@ -20899,7 +20905,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="13" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B84" s="15"/>
       <c r="C84" s="15"/>
@@ -20934,7 +20940,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="13" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B85" s="15"/>
       <c r="C85" s="15"/>
@@ -20975,7 +20981,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="13" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B86" s="15"/>
       <c r="C86" s="15"/>
@@ -21016,7 +21022,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="13" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B87" s="15"/>
       <c r="C87" s="15"/>
@@ -21061,7 +21067,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="13" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B88" s="15"/>
       <c r="C88" s="15"/>
@@ -21094,7 +21100,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="13" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B89" s="15"/>
       <c r="C89" s="15"/>
@@ -21125,7 +21131,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="13" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B90" s="15"/>
       <c r="C90" s="15"/>
@@ -21166,7 +21172,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="13" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B91" s="15"/>
       <c r="C91" s="15"/>
@@ -21199,7 +21205,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="13" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B92" s="15"/>
       <c r="C92" s="15"/>
@@ -21232,7 +21238,7 @@
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="17" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B93" s="24">
         <v>-71.76</v>
@@ -21303,7 +21309,7 @@
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="13" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B94" s="15"/>
       <c r="C94" s="15"/>
@@ -21332,7 +21338,7 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="17" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B95" s="19"/>
       <c r="C95" s="19"/>
@@ -21361,7 +21367,7 @@
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="13" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B96" s="14">
         <v>204.94</v>
@@ -21432,7 +21438,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="13" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B97" s="14">
         <v>149.55</v>
@@ -21503,7 +21509,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="13" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B98" s="15"/>
       <c r="C98" s="15"/>
@@ -21544,7 +21550,7 @@
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="13" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B99" s="21">
         <v>-55.38</v>
@@ -21599,7 +21605,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="17" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B100" s="19"/>
       <c r="C100" s="20">
@@ -22587,7 +22593,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -22757,22 +22763,22 @@
         <v>39</v>
       </c>
       <c r="W11" s="7" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AB11" s="7" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -23121,7 +23127,7 @@
     </row>
     <row r="17">
       <c r="A17" s="11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -23219,3169 +23225,3169 @@
         <v>69</v>
       </c>
       <c r="W18" s="12" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="X18" s="12" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Y18" s="12" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Z18" s="12" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AA18" s="12" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AB18" s="12" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="1">
-      <c r="A19" s="26" t="s">
-        <v>433</v>
-      </c>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="27"/>
-      <c r="K19" s="27"/>
-      <c r="L19" s="27"/>
-      <c r="M19" s="27"/>
-      <c r="N19" s="27"/>
-      <c r="O19" s="27"/>
-      <c r="P19" s="27"/>
-      <c r="Q19" s="27"/>
-      <c r="R19" s="27"/>
-      <c r="S19" s="27"/>
-      <c r="T19" s="27"/>
-      <c r="U19" s="27"/>
-      <c r="V19" s="27"/>
-      <c r="W19" s="27"/>
-      <c r="X19" s="27"/>
-      <c r="Y19" s="27"/>
-      <c r="Z19" s="27"/>
-      <c r="AA19" s="27"/>
-      <c r="AB19" s="27"/>
+      <c r="A19" s="27" t="s">
+        <v>434</v>
+      </c>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="28"/>
+      <c r="N19" s="28"/>
+      <c r="O19" s="28"/>
+      <c r="P19" s="28"/>
+      <c r="Q19" s="28"/>
+      <c r="R19" s="28"/>
+      <c r="S19" s="28"/>
+      <c r="T19" s="28"/>
+      <c r="U19" s="28"/>
+      <c r="V19" s="28"/>
+      <c r="W19" s="28"/>
+      <c r="X19" s="28"/>
+      <c r="Y19" s="28"/>
+      <c r="Z19" s="28"/>
+      <c r="AA19" s="28"/>
+      <c r="AB19" s="28"/>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="28" t="s">
-        <v>433</v>
-      </c>
-      <c r="B20" s="29">
+      <c r="A20" s="29" t="s">
+        <v>434</v>
+      </c>
+      <c r="B20" s="30">
         <v>959.85</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="30">
         <v>835.45</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="30">
         <v>494.43</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="30">
         <v>912.31</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="30">
         <v>295.62</v>
       </c>
-      <c r="G20" s="30">
+      <c r="G20" s="31">
         <v>-28.38</v>
       </c>
-      <c r="H20" s="29">
+      <c r="H20" s="30">
         <v>331.38</v>
       </c>
-      <c r="I20" s="29">
+      <c r="I20" s="30">
         <v>383.48</v>
       </c>
-      <c r="J20" s="29">
+      <c r="J20" s="30">
         <v>577.45</v>
       </c>
-      <c r="K20" s="29">
+      <c r="K20" s="30">
         <v>432.02</v>
       </c>
-      <c r="L20" s="29">
+      <c r="L20" s="30">
         <v>429.58</v>
       </c>
-      <c r="M20" s="29">
+      <c r="M20" s="30">
         <v>305.34</v>
       </c>
-      <c r="N20" s="29">
+      <c r="N20" s="30">
         <v>228.13</v>
       </c>
-      <c r="O20" s="29">
+      <c r="O20" s="30">
         <v>715.32</v>
       </c>
-      <c r="P20" s="29">
+      <c r="P20" s="30">
         <v>887.12</v>
       </c>
-      <c r="Q20" s="29">
+      <c r="Q20" s="30">
         <v>950.26</v>
       </c>
-      <c r="R20" s="29">
+      <c r="R20" s="30">
         <v>632.97</v>
       </c>
-      <c r="S20" s="29">
+      <c r="S20" s="30">
         <v>978.24</v>
       </c>
-      <c r="T20" s="29">
+      <c r="T20" s="30">
         <v>431.97</v>
       </c>
-      <c r="U20" s="29">
+      <c r="U20" s="30">
         <v>140.58</v>
       </c>
-      <c r="V20" s="29">
+      <c r="V20" s="30">
         <v>146.53</v>
       </c>
-      <c r="W20" s="31">
+      <c r="W20" s="32">
         <v>58.65</v>
       </c>
-      <c r="X20" s="31">
+      <c r="X20" s="32">
         <v>43.5</v>
       </c>
-      <c r="Y20" s="29">
+      <c r="Y20" s="30">
         <v>102.76</v>
       </c>
-      <c r="Z20" s="31">
+      <c r="Z20" s="32">
         <v>38.09</v>
       </c>
-      <c r="AA20" s="31">
+      <c r="AA20" s="32">
         <v>55.26</v>
       </c>
-      <c r="AB20" s="31">
+      <c r="AB20" s="32">
         <v>75.07</v>
       </c>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="28" t="s">
-        <v>434</v>
-      </c>
-      <c r="B21" s="29">
+      <c r="A21" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="B21" s="30">
         <v>699.53</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <v>501.89</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <v>401.07</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <v>378.88</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <v>311.91</v>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="30">
         <v>339.19</v>
       </c>
-      <c r="H21" s="29">
+      <c r="H21" s="30">
         <v>430.78</v>
       </c>
-      <c r="I21" s="29">
+      <c r="I21" s="30">
         <v>425.57</v>
       </c>
-      <c r="J21" s="29">
+      <c r="J21" s="30">
         <v>394.5</v>
       </c>
-      <c r="K21" s="29">
+      <c r="K21" s="30">
         <v>422.08</v>
       </c>
-      <c r="L21" s="29">
+      <c r="L21" s="30">
         <v>513.1</v>
       </c>
-      <c r="M21" s="29">
+      <c r="M21" s="30">
         <v>617.23</v>
       </c>
-      <c r="N21" s="29">
+      <c r="N21" s="30">
         <v>682.76</v>
       </c>
-      <c r="O21" s="29">
+      <c r="O21" s="30">
         <v>832.78</v>
       </c>
-      <c r="P21" s="29">
+      <c r="P21" s="30">
         <v>776.11</v>
       </c>
-      <c r="Q21" s="29">
+      <c r="Q21" s="30">
         <v>626.8</v>
       </c>
-      <c r="R21" s="29">
+      <c r="R21" s="30">
         <v>466.06</v>
       </c>
-      <c r="S21" s="29">
+      <c r="S21" s="30">
         <v>351.2</v>
       </c>
-      <c r="T21" s="29">
+      <c r="T21" s="30">
         <v>164.25</v>
       </c>
-      <c r="U21" s="31">
+      <c r="U21" s="32">
         <v>98.41</v>
       </c>
-      <c r="V21" s="31">
+      <c r="V21" s="32">
         <v>77.91</v>
       </c>
-      <c r="W21" s="31">
+      <c r="W21" s="32">
         <v>59.65</v>
       </c>
-      <c r="X21" s="31">
+      <c r="X21" s="32">
         <v>62.93</v>
       </c>
-      <c r="Y21" s="32"/>
-      <c r="Z21" s="32"/>
-      <c r="AA21" s="32"/>
-      <c r="AB21" s="32"/>
+      <c r="Y21" s="33"/>
+      <c r="Z21" s="33"/>
+      <c r="AA21" s="33"/>
+      <c r="AB21" s="33"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="26" t="s">
-        <v>435</v>
-      </c>
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="27"/>
-      <c r="J22" s="27"/>
-      <c r="K22" s="27"/>
-      <c r="L22" s="27"/>
-      <c r="M22" s="27"/>
-      <c r="N22" s="27"/>
-      <c r="O22" s="27"/>
-      <c r="P22" s="27"/>
-      <c r="Q22" s="27"/>
-      <c r="R22" s="27"/>
-      <c r="S22" s="27"/>
-      <c r="T22" s="27"/>
-      <c r="U22" s="27"/>
-      <c r="V22" s="27"/>
-      <c r="W22" s="27"/>
-      <c r="X22" s="27"/>
-      <c r="Y22" s="27"/>
-      <c r="Z22" s="27"/>
-      <c r="AA22" s="27"/>
-      <c r="AB22" s="27"/>
+      <c r="A22" s="27" t="s">
+        <v>436</v>
+      </c>
+      <c r="B22" s="28"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="28"/>
+      <c r="M22" s="28"/>
+      <c r="N22" s="28"/>
+      <c r="O22" s="28"/>
+      <c r="P22" s="28"/>
+      <c r="Q22" s="28"/>
+      <c r="R22" s="28"/>
+      <c r="S22" s="28"/>
+      <c r="T22" s="28"/>
+      <c r="U22" s="28"/>
+      <c r="V22" s="28"/>
+      <c r="W22" s="28"/>
+      <c r="X22" s="28"/>
+      <c r="Y22" s="28"/>
+      <c r="Z22" s="28"/>
+      <c r="AA22" s="28"/>
+      <c r="AB22" s="28"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="28" t="s">
-        <v>435</v>
-      </c>
-      <c r="B23" s="29">
+      <c r="A23" s="29" t="s">
+        <v>436</v>
+      </c>
+      <c r="B23" s="30">
         <v>1079.64</v>
       </c>
-      <c r="C23" s="29">
+      <c r="C23" s="30">
         <v>993.7</v>
       </c>
-      <c r="D23" s="29">
+      <c r="D23" s="30">
         <v>651.36</v>
       </c>
-      <c r="E23" s="29">
+      <c r="E23" s="30">
         <v>1061.74</v>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="30">
         <v>640.09</v>
       </c>
-      <c r="G23" s="29">
+      <c r="G23" s="30">
         <v>216.52</v>
       </c>
-      <c r="H23" s="29">
+      <c r="H23" s="30">
         <v>236.86</v>
       </c>
-      <c r="I23" s="29">
+      <c r="I23" s="30">
         <v>154.09</v>
       </c>
-      <c r="J23" s="29">
+      <c r="J23" s="30">
         <v>138.68</v>
       </c>
-      <c r="K23" s="29">
+      <c r="K23" s="30">
         <v>102.36</v>
       </c>
-      <c r="L23" s="29">
+      <c r="L23" s="30">
         <v>174.27</v>
       </c>
-      <c r="M23" s="29">
+      <c r="M23" s="30">
         <v>227.47</v>
       </c>
-      <c r="N23" s="29">
+      <c r="N23" s="30">
         <v>344.88</v>
       </c>
-      <c r="O23" s="29">
+      <c r="O23" s="30">
         <v>206.7</v>
       </c>
-      <c r="P23" s="29">
+      <c r="P23" s="30">
         <v>163.56</v>
       </c>
-      <c r="Q23" s="29">
+      <c r="Q23" s="30">
         <v>111.62</v>
       </c>
-      <c r="R23" s="29">
+      <c r="R23" s="30">
         <v>123.27</v>
       </c>
-      <c r="S23" s="29">
+      <c r="S23" s="30">
         <v>719.94</v>
       </c>
-      <c r="T23" s="29">
+      <c r="T23" s="30">
         <v>454.04</v>
       </c>
-      <c r="U23" s="29">
+      <c r="U23" s="30">
         <v>179.83</v>
       </c>
-      <c r="V23" s="31">
+      <c r="V23" s="32">
         <v>87.98</v>
       </c>
-      <c r="W23" s="31">
+      <c r="W23" s="32">
         <v>42.81</v>
       </c>
-      <c r="X23" s="31">
+      <c r="X23" s="32">
         <v>32.11</v>
       </c>
-      <c r="Y23" s="31">
+      <c r="Y23" s="32">
         <v>34.26</v>
       </c>
-      <c r="Z23" s="31">
+      <c r="Z23" s="32">
         <v>48.56</v>
       </c>
-      <c r="AA23" s="31">
+      <c r="AA23" s="32">
         <v>23.66</v>
       </c>
-      <c r="AB23" s="31">
+      <c r="AB23" s="32">
         <v>22.26</v>
       </c>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="28" t="s">
-        <v>436</v>
-      </c>
-      <c r="B24" s="29">
+      <c r="A24" s="29" t="s">
+        <v>437</v>
+      </c>
+      <c r="B24" s="30">
         <v>885.31</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C24" s="30">
         <v>712.68</v>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="30">
         <v>561.31</v>
       </c>
-      <c r="E24" s="29">
+      <c r="E24" s="30">
         <v>461.86</v>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="30">
         <v>277.25</v>
       </c>
-      <c r="G24" s="29">
+      <c r="G24" s="30">
         <v>169.7</v>
       </c>
-      <c r="H24" s="29">
+      <c r="H24" s="30">
         <v>161.25</v>
       </c>
-      <c r="I24" s="29">
+      <c r="I24" s="30">
         <v>159.38</v>
       </c>
-      <c r="J24" s="29">
+      <c r="J24" s="30">
         <v>197.53</v>
       </c>
-      <c r="K24" s="29">
+      <c r="K24" s="30">
         <v>211.14</v>
       </c>
-      <c r="L24" s="29">
+      <c r="L24" s="30">
         <v>223.38</v>
       </c>
-      <c r="M24" s="29">
+      <c r="M24" s="30">
         <v>210.85</v>
       </c>
-      <c r="N24" s="29">
+      <c r="N24" s="30">
         <v>190.01</v>
       </c>
-      <c r="O24" s="29">
+      <c r="O24" s="30">
         <v>265.02</v>
       </c>
-      <c r="P24" s="29">
+      <c r="P24" s="30">
         <v>314.49</v>
       </c>
-      <c r="Q24" s="29">
+      <c r="Q24" s="30">
         <v>317.74</v>
       </c>
-      <c r="R24" s="29">
+      <c r="R24" s="30">
         <v>313.01</v>
       </c>
-      <c r="S24" s="29">
+      <c r="S24" s="30">
         <v>296.92</v>
       </c>
-      <c r="T24" s="29">
+      <c r="T24" s="30">
         <v>159.35</v>
       </c>
-      <c r="U24" s="31">
+      <c r="U24" s="32">
         <v>75.4</v>
       </c>
-      <c r="V24" s="31">
+      <c r="V24" s="32">
         <v>49.14</v>
       </c>
-      <c r="W24" s="31">
+      <c r="W24" s="32">
         <v>36.28</v>
       </c>
-      <c r="X24" s="31">
+      <c r="X24" s="32">
         <v>32.17</v>
       </c>
-      <c r="Y24" s="32"/>
-      <c r="Z24" s="32"/>
-      <c r="AA24" s="32"/>
-      <c r="AB24" s="32"/>
+      <c r="Y24" s="33"/>
+      <c r="Z24" s="33"/>
+      <c r="AA24" s="33"/>
+      <c r="AB24" s="33"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="26" t="s">
-        <v>437</v>
-      </c>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
-      <c r="J25" s="27"/>
-      <c r="K25" s="27"/>
-      <c r="L25" s="27"/>
-      <c r="M25" s="27"/>
-      <c r="N25" s="27"/>
-      <c r="O25" s="27"/>
-      <c r="P25" s="27"/>
-      <c r="Q25" s="27"/>
-      <c r="R25" s="27"/>
-      <c r="S25" s="27"/>
-      <c r="T25" s="27"/>
-      <c r="U25" s="27"/>
-      <c r="V25" s="27"/>
-      <c r="W25" s="27"/>
-      <c r="X25" s="27"/>
-      <c r="Y25" s="27"/>
-      <c r="Z25" s="27"/>
-      <c r="AA25" s="27"/>
-      <c r="AB25" s="27"/>
+      <c r="A25" s="27" t="s">
+        <v>438</v>
+      </c>
+      <c r="B25" s="28"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+      <c r="M25" s="28"/>
+      <c r="N25" s="28"/>
+      <c r="O25" s="28"/>
+      <c r="P25" s="28"/>
+      <c r="Q25" s="28"/>
+      <c r="R25" s="28"/>
+      <c r="S25" s="28"/>
+      <c r="T25" s="28"/>
+      <c r="U25" s="28"/>
+      <c r="V25" s="28"/>
+      <c r="W25" s="28"/>
+      <c r="X25" s="28"/>
+      <c r="Y25" s="28"/>
+      <c r="Z25" s="28"/>
+      <c r="AA25" s="28"/>
+      <c r="AB25" s="28"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="28" t="s">
-        <v>438</v>
-      </c>
-      <c r="B26" s="31">
+      <c r="A26" s="29" t="s">
+        <v>439</v>
+      </c>
+      <c r="B26" s="32">
         <v>10.05</v>
       </c>
-      <c r="C26" s="31">
+      <c r="C26" s="32">
         <v>9.25</v>
       </c>
-      <c r="D26" s="31">
+      <c r="D26" s="32">
         <v>6.1</v>
       </c>
-      <c r="E26" s="31">
+      <c r="E26" s="32">
         <v>9.97</v>
       </c>
-      <c r="F26" s="31">
+      <c r="F26" s="32">
         <v>6.02</v>
       </c>
-      <c r="G26" s="31">
+      <c r="G26" s="32">
         <v>2.05</v>
       </c>
-      <c r="H26" s="31">
+      <c r="H26" s="32">
         <v>2.72</v>
       </c>
-      <c r="I26" s="31">
+      <c r="I26" s="32">
         <v>1.78</v>
       </c>
-      <c r="J26" s="31">
+      <c r="J26" s="32">
         <v>1.6</v>
       </c>
-      <c r="K26" s="31">
+      <c r="K26" s="32">
         <v>1.18</v>
       </c>
-      <c r="L26" s="31">
+      <c r="L26" s="32">
         <v>2.01</v>
       </c>
-      <c r="M26" s="31">
+      <c r="M26" s="32">
         <v>2.63</v>
       </c>
-      <c r="N26" s="31">
+      <c r="N26" s="32">
         <v>3.98</v>
       </c>
-      <c r="O26" s="31">
+      <c r="O26" s="32">
         <v>2.73</v>
       </c>
-      <c r="P26" s="31">
+      <c r="P26" s="32">
         <v>2.19</v>
       </c>
-      <c r="Q26" s="31">
+      <c r="Q26" s="32">
         <v>1.64</v>
       </c>
-      <c r="R26" s="31">
+      <c r="R26" s="32">
         <v>3.6</v>
       </c>
-      <c r="S26" s="31">
+      <c r="S26" s="32">
         <v>21.16</v>
       </c>
-      <c r="T26" s="31">
+      <c r="T26" s="32">
         <v>15.25</v>
       </c>
-      <c r="U26" s="31">
+      <c r="U26" s="32">
         <v>6.75</v>
       </c>
-      <c r="V26" s="31">
+      <c r="V26" s="32">
         <v>4.07</v>
       </c>
-      <c r="W26" s="31">
+      <c r="W26" s="32">
         <v>2.18</v>
       </c>
-      <c r="X26" s="31">
+      <c r="X26" s="32">
         <v>1.63</v>
       </c>
-      <c r="Y26" s="31">
+      <c r="Y26" s="32">
         <v>3.58</v>
       </c>
-      <c r="Z26" s="31">
+      <c r="Z26" s="32">
         <v>5.15</v>
       </c>
-      <c r="AA26" s="31">
+      <c r="AA26" s="32">
         <v>2.94</v>
       </c>
-      <c r="AB26" s="31">
+      <c r="AB26" s="32">
         <v>3.15</v>
       </c>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="28" t="s">
-        <v>439</v>
-      </c>
-      <c r="B27" s="31">
+      <c r="A27" s="29" t="s">
+        <v>440</v>
+      </c>
+      <c r="B27" s="32">
         <v>8.28</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="32">
         <v>6.68</v>
       </c>
-      <c r="D27" s="31">
+      <c r="D27" s="32">
         <v>5.37</v>
       </c>
-      <c r="E27" s="31">
+      <c r="E27" s="32">
         <v>4.51</v>
       </c>
-      <c r="F27" s="31">
+      <c r="F27" s="32">
         <v>2.83</v>
       </c>
-      <c r="G27" s="31">
+      <c r="G27" s="32">
         <v>1.87</v>
       </c>
-      <c r="H27" s="31">
+      <c r="H27" s="32">
         <v>1.86</v>
       </c>
-      <c r="I27" s="31">
+      <c r="I27" s="32">
         <v>1.84</v>
       </c>
-      <c r="J27" s="31">
+      <c r="J27" s="32">
         <v>2.28</v>
       </c>
-      <c r="K27" s="31">
+      <c r="K27" s="32">
         <v>2.51</v>
       </c>
-      <c r="L27" s="31">
+      <c r="L27" s="32">
         <v>2.71</v>
       </c>
-      <c r="M27" s="31">
+      <c r="M27" s="32">
         <v>2.63</v>
       </c>
-      <c r="N27" s="31">
+      <c r="N27" s="32">
         <v>2.83</v>
       </c>
-      <c r="O27" s="31">
+      <c r="O27" s="32">
         <v>6.26</v>
       </c>
-      <c r="P27" s="31">
+      <c r="P27" s="32">
         <v>8.77</v>
       </c>
-      <c r="Q27" s="31">
+      <c r="Q27" s="32">
         <v>9.68</v>
       </c>
-      <c r="R27" s="31">
+      <c r="R27" s="32">
         <v>10.17</v>
       </c>
-      <c r="S27" s="31">
+      <c r="S27" s="32">
         <v>9.88</v>
       </c>
-      <c r="T27" s="31">
+      <c r="T27" s="32">
         <v>5.98</v>
       </c>
-      <c r="U27" s="31">
+      <c r="U27" s="32">
         <v>3.64</v>
       </c>
-      <c r="V27" s="31">
+      <c r="V27" s="32">
         <v>3.32</v>
       </c>
-      <c r="W27" s="31">
+      <c r="W27" s="32">
         <v>3.1</v>
       </c>
-      <c r="X27" s="31">
+      <c r="X27" s="32">
         <v>3.29</v>
       </c>
-      <c r="Y27" s="32"/>
-      <c r="Z27" s="32"/>
-      <c r="AA27" s="32"/>
-      <c r="AB27" s="32"/>
+      <c r="Y27" s="33"/>
+      <c r="Z27" s="33"/>
+      <c r="AA27" s="33"/>
+      <c r="AB27" s="33"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="26" t="s">
-        <v>440</v>
-      </c>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="27"/>
-      <c r="J28" s="27"/>
-      <c r="K28" s="27"/>
-      <c r="L28" s="27"/>
-      <c r="M28" s="27"/>
-      <c r="N28" s="27"/>
-      <c r="O28" s="27"/>
-      <c r="P28" s="27"/>
-      <c r="Q28" s="27"/>
-      <c r="R28" s="27"/>
-      <c r="S28" s="27"/>
-      <c r="T28" s="27"/>
-      <c r="U28" s="27"/>
-      <c r="V28" s="27"/>
-      <c r="W28" s="27"/>
-      <c r="X28" s="27"/>
-      <c r="Y28" s="27"/>
-      <c r="Z28" s="27"/>
-      <c r="AA28" s="27"/>
-      <c r="AB28" s="27"/>
+      <c r="A28" s="27" t="s">
+        <v>441</v>
+      </c>
+      <c r="B28" s="28"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+      <c r="M28" s="28"/>
+      <c r="N28" s="28"/>
+      <c r="O28" s="28"/>
+      <c r="P28" s="28"/>
+      <c r="Q28" s="28"/>
+      <c r="R28" s="28"/>
+      <c r="S28" s="28"/>
+      <c r="T28" s="28"/>
+      <c r="U28" s="28"/>
+      <c r="V28" s="28"/>
+      <c r="W28" s="28"/>
+      <c r="X28" s="28"/>
+      <c r="Y28" s="28"/>
+      <c r="Z28" s="28"/>
+      <c r="AA28" s="28"/>
+      <c r="AB28" s="28"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="28" t="s">
-        <v>441</v>
-      </c>
-      <c r="B29" s="33">
+      <c r="A29" s="29" t="s">
+        <v>442</v>
+      </c>
+      <c r="B29" s="34">
         <v>11.49</v>
       </c>
-      <c r="C29" s="33">
+      <c r="C29" s="34">
         <v>5.8</v>
       </c>
-      <c r="D29" s="33">
+      <c r="D29" s="34">
         <v>0.99</v>
       </c>
-      <c r="E29" s="34">
+      <c r="E29" s="35">
         <v>-7.63</v>
       </c>
-      <c r="F29" s="33">
+      <c r="F29" s="34">
         <v>18.04</v>
       </c>
-      <c r="G29" s="33">
+      <c r="G29" s="34">
         <v>22.24</v>
       </c>
-      <c r="H29" s="33">
+      <c r="H29" s="34">
         <v>48.55</v>
       </c>
-      <c r="I29" s="33">
+      <c r="I29" s="34">
         <v>14.71</v>
       </c>
-      <c r="J29" s="34">
+      <c r="J29" s="35">
         <v>-99.77</v>
       </c>
-      <c r="K29" s="34">
+      <c r="K29" s="35">
         <v>-76.17</v>
       </c>
-      <c r="L29" s="34">
+      <c r="L29" s="35">
         <v>-140.95</v>
       </c>
-      <c r="M29" s="34">
+      <c r="M29" s="35">
         <v>-90.72</v>
       </c>
-      <c r="N29" s="34">
+      <c r="N29" s="35">
         <v>-23.85</v>
       </c>
-      <c r="O29" s="33">
+      <c r="O29" s="34">
         <v>31.83</v>
       </c>
-      <c r="P29" s="34">
+      <c r="P29" s="35">
         <v>-5.67</v>
       </c>
-      <c r="Q29" s="34">
+      <c r="Q29" s="35">
         <v>-770.09</v>
       </c>
-      <c r="R29" s="34">
+      <c r="R29" s="35">
         <v>-118.47</v>
       </c>
-      <c r="S29" s="33">
+      <c r="S29" s="34">
         <v>3.45</v>
       </c>
-      <c r="T29" s="34">
+      <c r="T29" s="35">
         <v>-1.62</v>
       </c>
-      <c r="U29" s="34">
+      <c r="U29" s="35">
         <v>-52.59</v>
       </c>
-      <c r="V29" s="34">
+      <c r="V29" s="35">
         <v>-37.39</v>
       </c>
-      <c r="W29" s="33">
+      <c r="W29" s="34">
         <v>18.9</v>
       </c>
-      <c r="X29" s="34">
+      <c r="X29" s="35">
         <v>-150.66</v>
       </c>
-      <c r="Y29" s="34">
+      <c r="Y29" s="35">
         <v>-382.27</v>
       </c>
-      <c r="Z29" s="33">
+      <c r="Z29" s="34">
         <v>6.22</v>
       </c>
-      <c r="AA29" s="33">
+      <c r="AA29" s="34">
         <v>38.21</v>
       </c>
-      <c r="AB29" s="34">
+      <c r="AB29" s="35">
         <v>-78.41</v>
       </c>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="28" t="s">
-        <v>442</v>
-      </c>
-      <c r="B30" s="33">
+      <c r="A30" s="29" t="s">
+        <v>443</v>
+      </c>
+      <c r="B30" s="34">
         <v>5.02</v>
       </c>
-      <c r="C30" s="33">
+      <c r="C30" s="34">
         <v>4.13</v>
       </c>
-      <c r="D30" s="33">
+      <c r="D30" s="34">
         <v>8.05</v>
       </c>
-      <c r="E30" s="33">
+      <c r="E30" s="34">
         <v>10.49</v>
       </c>
-      <c r="F30" s="33">
+      <c r="F30" s="34">
         <v>10.77</v>
       </c>
-      <c r="G30" s="34">
+      <c r="G30" s="35">
         <v>-4.93</v>
       </c>
-      <c r="H30" s="34">
+      <c r="H30" s="35">
         <v>-40.37</v>
       </c>
-      <c r="I30" s="34">
+      <c r="I30" s="35">
         <v>-81.03</v>
       </c>
-      <c r="J30" s="34">
+      <c r="J30" s="35">
         <v>-76.0</v>
       </c>
-      <c r="K30" s="34">
+      <c r="K30" s="35">
         <v>-49.46</v>
       </c>
-      <c r="L30" s="34">
+      <c r="L30" s="35">
         <v>-40.05</v>
       </c>
-      <c r="M30" s="34">
+      <c r="M30" s="35">
         <v>-115.72</v>
       </c>
-      <c r="N30" s="34">
+      <c r="N30" s="35">
         <v>-121.06</v>
       </c>
-      <c r="O30" s="34">
+      <c r="O30" s="35">
         <v>-49.32</v>
       </c>
-      <c r="P30" s="34">
+      <c r="P30" s="35">
         <v>-37.78</v>
       </c>
-      <c r="Q30" s="34">
+      <c r="Q30" s="35">
         <v>-41.3</v>
       </c>
-      <c r="R30" s="34">
+      <c r="R30" s="35">
         <v>-17.42</v>
       </c>
-      <c r="S30" s="34">
+      <c r="S30" s="35">
         <v>-8.46</v>
       </c>
-      <c r="T30" s="34">
+      <c r="T30" s="35">
         <v>-24.66</v>
       </c>
-      <c r="U30" s="34">
+      <c r="U30" s="35">
         <v>-114.15</v>
       </c>
-      <c r="V30" s="34">
+      <c r="V30" s="35">
         <v>-101.84</v>
       </c>
-      <c r="W30" s="34">
+      <c r="W30" s="35">
         <v>-92.16</v>
       </c>
-      <c r="X30" s="34">
+      <c r="X30" s="35">
         <v>-104.23</v>
       </c>
-      <c r="Y30" s="33"/>
-      <c r="Z30" s="33"/>
-      <c r="AA30" s="33"/>
-      <c r="AB30" s="33"/>
+      <c r="Y30" s="34"/>
+      <c r="Z30" s="34"/>
+      <c r="AA30" s="34"/>
+      <c r="AB30" s="34"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="26" t="s">
-        <v>443</v>
-      </c>
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="27"/>
-      <c r="J31" s="27"/>
-      <c r="K31" s="27"/>
-      <c r="L31" s="27"/>
-      <c r="M31" s="27"/>
-      <c r="N31" s="27"/>
-      <c r="O31" s="27"/>
-      <c r="P31" s="27"/>
-      <c r="Q31" s="27"/>
-      <c r="R31" s="27"/>
-      <c r="S31" s="27"/>
-      <c r="T31" s="27"/>
-      <c r="U31" s="27"/>
-      <c r="V31" s="27"/>
-      <c r="W31" s="27"/>
-      <c r="X31" s="27"/>
-      <c r="Y31" s="27"/>
-      <c r="Z31" s="27"/>
-      <c r="AA31" s="27"/>
-      <c r="AB31" s="27"/>
+      <c r="A31" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B31" s="28"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
+      <c r="I31" s="28"/>
+      <c r="J31" s="28"/>
+      <c r="K31" s="28"/>
+      <c r="L31" s="28"/>
+      <c r="M31" s="28"/>
+      <c r="N31" s="28"/>
+      <c r="O31" s="28"/>
+      <c r="P31" s="28"/>
+      <c r="Q31" s="28"/>
+      <c r="R31" s="28"/>
+      <c r="S31" s="28"/>
+      <c r="T31" s="28"/>
+      <c r="U31" s="28"/>
+      <c r="V31" s="28"/>
+      <c r="W31" s="28"/>
+      <c r="X31" s="28"/>
+      <c r="Y31" s="28"/>
+      <c r="Z31" s="28"/>
+      <c r="AA31" s="28"/>
+      <c r="AB31" s="28"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="28" t="s">
-        <v>444</v>
-      </c>
-      <c r="B32" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="C32" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="D32" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="E32" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="F32" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="G32" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="H32" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="I32" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="J32" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="K32" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="L32" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="M32" s="33">
+      <c r="A32" s="29" t="s">
+        <v>445</v>
+      </c>
+      <c r="B32" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="C32" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="D32" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="E32" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="F32" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="G32" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="H32" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="I32" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="J32" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="K32" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="L32" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="M32" s="34">
         <v>27.41</v>
       </c>
-      <c r="N32" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="O32" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="P32" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="Q32" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="R32" s="33">
+      <c r="N32" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="O32" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="P32" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="Q32" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="R32" s="34">
         <v>18.92</v>
       </c>
-      <c r="S32" s="33">
+      <c r="S32" s="34">
         <v>2.57</v>
       </c>
-      <c r="T32" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="U32" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="V32" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="W32" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="X32" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="Y32" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="Z32" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="AA32" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="AB32" s="33">
+      <c r="T32" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="U32" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="V32" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="W32" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="X32" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="Y32" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="Z32" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="AA32" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="AB32" s="34">
         <v>0.0</v>
       </c>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="28" t="s">
-        <v>445</v>
-      </c>
-      <c r="B33" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="C33" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="D33" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="E33" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="F33" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="G33" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="H33" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="I33" s="33">
+      <c r="A33" s="29" t="s">
+        <v>446</v>
+      </c>
+      <c r="B33" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="C33" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="D33" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="E33" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="F33" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="G33" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="H33" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="I33" s="34">
         <v>7.83</v>
       </c>
-      <c r="J33" s="33">
+      <c r="J33" s="34">
         <v>6.31</v>
       </c>
-      <c r="K33" s="33">
+      <c r="K33" s="34">
         <v>5.74</v>
       </c>
-      <c r="L33" s="33">
+      <c r="L33" s="34">
         <v>5.32</v>
       </c>
-      <c r="M33" s="33">
+      <c r="M33" s="34">
         <v>5.46</v>
       </c>
-      <c r="N33" s="33">
+      <c r="N33" s="34">
         <v>4.81</v>
       </c>
-      <c r="O33" s="33">
+      <c r="O33" s="34">
         <v>3.91</v>
       </c>
-      <c r="P33" s="33">
+      <c r="P33" s="34">
         <v>2.79</v>
       </c>
-      <c r="Q33" s="33">
+      <c r="Q33" s="34">
         <v>2.53</v>
       </c>
-      <c r="R33" s="33">
+      <c r="R33" s="34">
         <v>2.41</v>
       </c>
-      <c r="S33" s="33">
+      <c r="S33" s="34">
         <v>1.1</v>
       </c>
-      <c r="T33" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="U33" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="V33" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="W33" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="X33" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="Y33" s="33"/>
-      <c r="Z33" s="33"/>
-      <c r="AA33" s="33"/>
-      <c r="AB33" s="33"/>
+      <c r="T33" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="U33" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="V33" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="W33" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="X33" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="Y33" s="34"/>
+      <c r="Z33" s="34"/>
+      <c r="AA33" s="34"/>
+      <c r="AB33" s="34"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="28" t="s">
-        <v>446</v>
-      </c>
-      <c r="B34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="C34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="D34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="E34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="F34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="G34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="H34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="I34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="J34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="K34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="L34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="M34" s="33">
+      <c r="A34" s="29" t="s">
+        <v>447</v>
+      </c>
+      <c r="B34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="C34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="D34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="E34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="F34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="G34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="H34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="I34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="J34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="K34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="L34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="M34" s="34">
         <v>38.07</v>
       </c>
-      <c r="N34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="O34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="P34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="Q34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="R34" s="33">
+      <c r="N34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="O34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="P34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="Q34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="R34" s="34">
         <v>26.27</v>
       </c>
-      <c r="S34" s="33">
+      <c r="S34" s="34">
         <v>3.57</v>
       </c>
-      <c r="T34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="U34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="V34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="W34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="X34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="Y34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="Z34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="AA34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="AB34" s="33">
+      <c r="T34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="U34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="V34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="W34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="X34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="Y34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="Z34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="AA34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="AB34" s="34">
         <v>0.0</v>
       </c>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="28" t="s">
-        <v>447</v>
-      </c>
-      <c r="B35" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="C35" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="D35" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="E35" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="F35" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="G35" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="H35" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="I35" s="33">
+      <c r="A35" s="29" t="s">
+        <v>448</v>
+      </c>
+      <c r="B35" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="C35" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="D35" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="E35" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="F35" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="G35" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="H35" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="I35" s="34">
         <v>10.87</v>
       </c>
-      <c r="J35" s="33">
+      <c r="J35" s="34">
         <v>8.77</v>
       </c>
-      <c r="K35" s="33">
+      <c r="K35" s="34">
         <v>7.98</v>
       </c>
-      <c r="L35" s="33">
+      <c r="L35" s="34">
         <v>7.38</v>
       </c>
-      <c r="M35" s="33">
+      <c r="M35" s="34">
         <v>7.59</v>
       </c>
-      <c r="N35" s="33">
+      <c r="N35" s="34">
         <v>6.68</v>
       </c>
-      <c r="O35" s="33">
+      <c r="O35" s="34">
         <v>5.43</v>
       </c>
-      <c r="P35" s="33">
+      <c r="P35" s="34">
         <v>3.88</v>
       </c>
-      <c r="Q35" s="33">
+      <c r="Q35" s="34">
         <v>3.51</v>
       </c>
-      <c r="R35" s="33">
+      <c r="R35" s="34">
         <v>3.35</v>
       </c>
-      <c r="S35" s="33">
+      <c r="S35" s="34">
         <v>1.53</v>
       </c>
-      <c r="T35" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="U35" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="V35" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="W35" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="X35" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="Y35" s="33"/>
-      <c r="Z35" s="33"/>
-      <c r="AA35" s="33"/>
-      <c r="AB35" s="33"/>
+      <c r="T35" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="U35" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="V35" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="W35" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="X35" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="Y35" s="34"/>
+      <c r="Z35" s="34"/>
+      <c r="AA35" s="34"/>
+      <c r="AB35" s="34"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="26" t="s">
-        <v>448</v>
-      </c>
-      <c r="B36" s="27"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="27"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="27"/>
-      <c r="H36" s="27"/>
-      <c r="I36" s="27"/>
-      <c r="J36" s="27"/>
-      <c r="K36" s="27"/>
-      <c r="L36" s="27"/>
-      <c r="M36" s="27"/>
-      <c r="N36" s="27"/>
-      <c r="O36" s="27"/>
-      <c r="P36" s="27"/>
-      <c r="Q36" s="27"/>
-      <c r="R36" s="27"/>
-      <c r="S36" s="27"/>
-      <c r="T36" s="27"/>
-      <c r="U36" s="27"/>
-      <c r="V36" s="27"/>
-      <c r="W36" s="27"/>
-      <c r="X36" s="27"/>
-      <c r="Y36" s="27"/>
-      <c r="Z36" s="27"/>
-      <c r="AA36" s="27"/>
-      <c r="AB36" s="27"/>
+      <c r="A36" s="27" t="s">
+        <v>449</v>
+      </c>
+      <c r="B36" s="28"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="28"/>
+      <c r="J36" s="28"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+      <c r="M36" s="28"/>
+      <c r="N36" s="28"/>
+      <c r="O36" s="28"/>
+      <c r="P36" s="28"/>
+      <c r="Q36" s="28"/>
+      <c r="R36" s="28"/>
+      <c r="S36" s="28"/>
+      <c r="T36" s="28"/>
+      <c r="U36" s="28"/>
+      <c r="V36" s="28"/>
+      <c r="W36" s="28"/>
+      <c r="X36" s="28"/>
+      <c r="Y36" s="28"/>
+      <c r="Z36" s="28"/>
+      <c r="AA36" s="28"/>
+      <c r="AB36" s="28"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="28" t="s">
-        <v>449</v>
-      </c>
-      <c r="B37" s="31">
+      <c r="A37" s="29" t="s">
+        <v>450</v>
+      </c>
+      <c r="B37" s="32">
         <v>2.48</v>
       </c>
-      <c r="C37" s="31">
+      <c r="C37" s="32">
         <v>2.43</v>
       </c>
-      <c r="D37" s="31">
+      <c r="D37" s="32">
         <v>1.97</v>
       </c>
-      <c r="E37" s="31">
+      <c r="E37" s="32">
         <v>3.58</v>
       </c>
-      <c r="F37" s="31">
+      <c r="F37" s="32">
         <v>3.45</v>
       </c>
-      <c r="G37" s="31">
+      <c r="G37" s="32">
         <v>1.0</v>
       </c>
-      <c r="H37" s="31">
+      <c r="H37" s="32">
         <v>0.66</v>
       </c>
-      <c r="I37" s="31">
+      <c r="I37" s="32">
         <v>0.34</v>
       </c>
-      <c r="J37" s="31">
+      <c r="J37" s="32">
         <v>0.29</v>
       </c>
-      <c r="K37" s="31">
+      <c r="K37" s="32">
         <v>0.16</v>
       </c>
-      <c r="L37" s="31">
+      <c r="L37" s="32">
         <v>0.29</v>
       </c>
-      <c r="M37" s="31">
+      <c r="M37" s="32">
         <v>0.4</v>
       </c>
-      <c r="N37" s="31">
+      <c r="N37" s="32">
         <v>0.43</v>
       </c>
-      <c r="O37" s="31">
+      <c r="O37" s="32">
         <v>0.25</v>
       </c>
-      <c r="P37" s="31">
+      <c r="P37" s="32">
         <v>0.2</v>
       </c>
-      <c r="Q37" s="31">
+      <c r="Q37" s="32">
         <v>0.12</v>
       </c>
-      <c r="R37" s="31">
+      <c r="R37" s="32">
         <v>0.12</v>
       </c>
-      <c r="S37" s="31">
+      <c r="S37" s="32">
         <v>0.77</v>
       </c>
-      <c r="T37" s="31">
+      <c r="T37" s="32">
         <v>0.76</v>
       </c>
-      <c r="U37" s="31">
+      <c r="U37" s="32">
         <v>0.46</v>
       </c>
-      <c r="V37" s="31">
+      <c r="V37" s="32">
         <v>0.34</v>
       </c>
-      <c r="W37" s="31">
+      <c r="W37" s="32">
         <v>0.19</v>
       </c>
-      <c r="X37" s="31">
+      <c r="X37" s="32">
         <v>0.15</v>
       </c>
-      <c r="Y37" s="31">
+      <c r="Y37" s="32">
         <v>0.32</v>
       </c>
-      <c r="Z37" s="31">
+      <c r="Z37" s="32">
         <v>0.48</v>
       </c>
-      <c r="AA37" s="31">
+      <c r="AA37" s="32">
         <v>0.29</v>
       </c>
-      <c r="AB37" s="31">
+      <c r="AB37" s="32">
         <v>0.36</v>
       </c>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="28" t="s">
-        <v>450</v>
-      </c>
-      <c r="B38" s="31">
+      <c r="A38" s="29" t="s">
+        <v>451</v>
+      </c>
+      <c r="B38" s="32">
         <v>2.67</v>
       </c>
-      <c r="C38" s="31">
+      <c r="C38" s="32">
         <v>2.47</v>
       </c>
-      <c r="D38" s="31">
+      <c r="D38" s="32">
         <v>1.95</v>
       </c>
-      <c r="E38" s="31">
+      <c r="E38" s="32">
         <v>1.41</v>
       </c>
-      <c r="F38" s="31">
+      <c r="F38" s="32">
         <v>0.76</v>
       </c>
-      <c r="G38" s="31">
+      <c r="G38" s="32">
         <v>0.39</v>
       </c>
-      <c r="H38" s="31">
+      <c r="H38" s="32">
         <v>0.32</v>
       </c>
-      <c r="I38" s="31">
+      <c r="I38" s="32">
         <v>0.29</v>
       </c>
-      <c r="J38" s="31">
+      <c r="J38" s="32">
         <v>0.32</v>
       </c>
-      <c r="K38" s="31">
+      <c r="K38" s="32">
         <v>0.3</v>
       </c>
-      <c r="L38" s="31">
+      <c r="L38" s="32">
         <v>0.3</v>
       </c>
-      <c r="M38" s="31">
+      <c r="M38" s="32">
         <v>0.26</v>
       </c>
-      <c r="N38" s="31">
+      <c r="N38" s="32">
         <v>0.19</v>
       </c>
-      <c r="O38" s="31">
+      <c r="O38" s="32">
         <v>0.34</v>
       </c>
-      <c r="P38" s="31">
+      <c r="P38" s="32">
         <v>0.43</v>
       </c>
-      <c r="Q38" s="31">
+      <c r="Q38" s="32">
         <v>0.46</v>
       </c>
-      <c r="R38" s="31">
+      <c r="R38" s="32">
         <v>0.49</v>
       </c>
-      <c r="S38" s="31">
+      <c r="S38" s="32">
         <v>0.58</v>
       </c>
-      <c r="T38" s="31">
+      <c r="T38" s="32">
         <v>0.43</v>
       </c>
-      <c r="U38" s="31">
+      <c r="U38" s="32">
         <v>0.3</v>
       </c>
-      <c r="V38" s="31">
+      <c r="V38" s="32">
         <v>0.3</v>
       </c>
-      <c r="W38" s="31">
+      <c r="W38" s="32">
         <v>0.29</v>
       </c>
-      <c r="X38" s="31">
+      <c r="X38" s="32">
         <v>0.32</v>
       </c>
-      <c r="Y38" s="32"/>
-      <c r="Z38" s="32"/>
-      <c r="AA38" s="32"/>
-      <c r="AB38" s="32"/>
+      <c r="Y38" s="33"/>
+      <c r="Z38" s="33"/>
+      <c r="AA38" s="33"/>
+      <c r="AB38" s="33"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="26" t="s">
-        <v>451</v>
-      </c>
-      <c r="B39" s="27"/>
-      <c r="C39" s="27"/>
-      <c r="D39" s="27"/>
-      <c r="E39" s="27"/>
-      <c r="F39" s="27"/>
-      <c r="G39" s="27"/>
-      <c r="H39" s="27"/>
-      <c r="I39" s="27"/>
-      <c r="J39" s="27"/>
-      <c r="K39" s="27"/>
-      <c r="L39" s="27"/>
-      <c r="M39" s="27"/>
-      <c r="N39" s="27"/>
-      <c r="O39" s="27"/>
-      <c r="P39" s="27"/>
-      <c r="Q39" s="27"/>
-      <c r="R39" s="27"/>
-      <c r="S39" s="27"/>
-      <c r="T39" s="27"/>
-      <c r="U39" s="27"/>
-      <c r="V39" s="27"/>
-      <c r="W39" s="27"/>
-      <c r="X39" s="27"/>
-      <c r="Y39" s="27"/>
-      <c r="Z39" s="27"/>
-      <c r="AA39" s="27"/>
-      <c r="AB39" s="27"/>
+      <c r="A39" s="27" t="s">
+        <v>452</v>
+      </c>
+      <c r="B39" s="28"/>
+      <c r="C39" s="28"/>
+      <c r="D39" s="28"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="28"/>
+      <c r="I39" s="28"/>
+      <c r="J39" s="28"/>
+      <c r="K39" s="28"/>
+      <c r="L39" s="28"/>
+      <c r="M39" s="28"/>
+      <c r="N39" s="28"/>
+      <c r="O39" s="28"/>
+      <c r="P39" s="28"/>
+      <c r="Q39" s="28"/>
+      <c r="R39" s="28"/>
+      <c r="S39" s="28"/>
+      <c r="T39" s="28"/>
+      <c r="U39" s="28"/>
+      <c r="V39" s="28"/>
+      <c r="W39" s="28"/>
+      <c r="X39" s="28"/>
+      <c r="Y39" s="28"/>
+      <c r="Z39" s="28"/>
+      <c r="AA39" s="28"/>
+      <c r="AB39" s="28"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="28" t="s">
-        <v>452</v>
-      </c>
-      <c r="B40" s="31">
+      <c r="A40" s="29" t="s">
+        <v>453</v>
+      </c>
+      <c r="B40" s="32">
         <v>4.81</v>
       </c>
-      <c r="C40" s="31">
+      <c r="C40" s="32">
         <v>2.91</v>
       </c>
-      <c r="D40" s="31">
+      <c r="D40" s="32">
         <v>2.54</v>
       </c>
-      <c r="E40" s="31">
+      <c r="E40" s="32">
         <v>4.42</v>
       </c>
-      <c r="F40" s="31">
+      <c r="F40" s="32">
         <v>4.5</v>
       </c>
-      <c r="G40" s="31">
+      <c r="G40" s="32">
         <v>1.18</v>
       </c>
-      <c r="H40" s="31">
+      <c r="H40" s="32">
         <v>0.67</v>
       </c>
-      <c r="I40" s="31">
+      <c r="I40" s="32">
         <v>0.34</v>
       </c>
-      <c r="J40" s="32"/>
-      <c r="K40" s="32"/>
-      <c r="L40" s="32"/>
-      <c r="M40" s="32"/>
-      <c r="N40" s="31">
+      <c r="J40" s="33"/>
+      <c r="K40" s="33"/>
+      <c r="L40" s="33"/>
+      <c r="M40" s="33"/>
+      <c r="N40" s="32">
         <v>1.42</v>
       </c>
-      <c r="O40" s="32"/>
-      <c r="P40" s="32"/>
-      <c r="Q40" s="31">
+      <c r="O40" s="33"/>
+      <c r="P40" s="33"/>
+      <c r="Q40" s="32">
         <v>1.09</v>
       </c>
-      <c r="R40" s="32"/>
-      <c r="S40" s="31">
+      <c r="R40" s="33"/>
+      <c r="S40" s="32">
         <v>9.36</v>
       </c>
-      <c r="T40" s="31">
+      <c r="T40" s="32">
         <v>1.56</v>
       </c>
-      <c r="U40" s="31">
+      <c r="U40" s="32">
         <v>0.46</v>
       </c>
-      <c r="V40" s="32"/>
-      <c r="W40" s="32"/>
-      <c r="X40" s="32"/>
-      <c r="Y40" s="32"/>
-      <c r="Z40" s="31">
+      <c r="V40" s="33"/>
+      <c r="W40" s="33"/>
+      <c r="X40" s="33"/>
+      <c r="Y40" s="33"/>
+      <c r="Z40" s="32">
         <v>0.48</v>
       </c>
-      <c r="AA40" s="31">
+      <c r="AA40" s="32">
         <v>0.42</v>
       </c>
-      <c r="AB40" s="31">
+      <c r="AB40" s="32">
         <v>0.58</v>
       </c>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="28" t="s">
-        <v>453</v>
-      </c>
-      <c r="B41" s="31">
+      <c r="A41" s="29" t="s">
+        <v>454</v>
+      </c>
+      <c r="B41" s="32">
         <v>3.67</v>
       </c>
-      <c r="C41" s="31">
+      <c r="C41" s="32">
         <v>3.06</v>
       </c>
-      <c r="D41" s="31">
+      <c r="D41" s="32">
         <v>2.28</v>
       </c>
-      <c r="E41" s="31">
+      <c r="E41" s="32">
         <v>1.55</v>
       </c>
-      <c r="F41" s="31">
+      <c r="F41" s="32">
         <v>1.43</v>
       </c>
-      <c r="G41" s="31">
+      <c r="G41" s="32">
         <v>1.52</v>
       </c>
-      <c r="H41" s="31">
+      <c r="H41" s="32">
         <v>2.24</v>
       </c>
-      <c r="I41" s="32"/>
-      <c r="J41" s="32"/>
-      <c r="K41" s="32"/>
-      <c r="L41" s="32"/>
-      <c r="M41" s="32"/>
-      <c r="N41" s="32"/>
-      <c r="O41" s="32"/>
-      <c r="P41" s="31">
+      <c r="I41" s="33"/>
+      <c r="J41" s="33"/>
+      <c r="K41" s="33"/>
+      <c r="L41" s="33"/>
+      <c r="M41" s="33"/>
+      <c r="N41" s="33"/>
+      <c r="O41" s="33"/>
+      <c r="P41" s="32">
         <v>6.41</v>
       </c>
-      <c r="Q41" s="31">
+      <c r="Q41" s="32">
         <v>2.19</v>
       </c>
-      <c r="R41" s="31">
+      <c r="R41" s="32">
         <v>2.48</v>
       </c>
-      <c r="S41" s="31">
+      <c r="S41" s="32">
         <v>1.87</v>
       </c>
-      <c r="T41" s="31">
+      <c r="T41" s="32">
         <v>1.3</v>
       </c>
-      <c r="U41" s="32"/>
-      <c r="V41" s="32"/>
-      <c r="W41" s="31">
+      <c r="U41" s="33"/>
+      <c r="V41" s="33"/>
+      <c r="W41" s="32">
         <v>8.21</v>
       </c>
-      <c r="X41" s="31">
+      <c r="X41" s="32">
         <v>2.17</v>
       </c>
-      <c r="Y41" s="32"/>
-      <c r="Z41" s="32"/>
-      <c r="AA41" s="32"/>
-      <c r="AB41" s="32"/>
+      <c r="Y41" s="33"/>
+      <c r="Z41" s="33"/>
+      <c r="AA41" s="33"/>
+      <c r="AB41" s="33"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="26" t="s">
-        <v>454</v>
-      </c>
-      <c r="B42" s="27"/>
-      <c r="C42" s="27"/>
-      <c r="D42" s="27"/>
-      <c r="E42" s="27"/>
-      <c r="F42" s="27"/>
-      <c r="G42" s="27"/>
-      <c r="H42" s="27"/>
-      <c r="I42" s="27"/>
-      <c r="J42" s="27"/>
-      <c r="K42" s="27"/>
-      <c r="L42" s="27"/>
-      <c r="M42" s="27"/>
-      <c r="N42" s="27"/>
-      <c r="O42" s="27"/>
-      <c r="P42" s="27"/>
-      <c r="Q42" s="27"/>
-      <c r="R42" s="27"/>
-      <c r="S42" s="27"/>
-      <c r="T42" s="27"/>
-      <c r="U42" s="27"/>
-      <c r="V42" s="27"/>
-      <c r="W42" s="27"/>
-      <c r="X42" s="27"/>
-      <c r="Y42" s="27"/>
-      <c r="Z42" s="27"/>
-      <c r="AA42" s="27"/>
-      <c r="AB42" s="27"/>
+      <c r="A42" s="27" t="s">
+        <v>455</v>
+      </c>
+      <c r="B42" s="28"/>
+      <c r="C42" s="28"/>
+      <c r="D42" s="28"/>
+      <c r="E42" s="28"/>
+      <c r="F42" s="28"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="28"/>
+      <c r="I42" s="28"/>
+      <c r="J42" s="28"/>
+      <c r="K42" s="28"/>
+      <c r="L42" s="28"/>
+      <c r="M42" s="28"/>
+      <c r="N42" s="28"/>
+      <c r="O42" s="28"/>
+      <c r="P42" s="28"/>
+      <c r="Q42" s="28"/>
+      <c r="R42" s="28"/>
+      <c r="S42" s="28"/>
+      <c r="T42" s="28"/>
+      <c r="U42" s="28"/>
+      <c r="V42" s="28"/>
+      <c r="W42" s="28"/>
+      <c r="X42" s="28"/>
+      <c r="Y42" s="28"/>
+      <c r="Z42" s="28"/>
+      <c r="AA42" s="28"/>
+      <c r="AB42" s="28"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="28" t="s">
-        <v>455</v>
-      </c>
-      <c r="B43" s="31">
+      <c r="A43" s="29" t="s">
+        <v>456</v>
+      </c>
+      <c r="B43" s="32">
         <v>1.63</v>
       </c>
-      <c r="C43" s="31">
+      <c r="C43" s="32">
         <v>1.68</v>
       </c>
-      <c r="D43" s="31">
+      <c r="D43" s="32">
         <v>1.67</v>
       </c>
-      <c r="E43" s="31">
+      <c r="E43" s="32">
         <v>2.21</v>
       </c>
-      <c r="F43" s="31">
+      <c r="F43" s="32">
         <v>1.77</v>
       </c>
-      <c r="G43" s="31">
+      <c r="G43" s="32">
         <v>0.81</v>
       </c>
-      <c r="H43" s="31">
+      <c r="H43" s="32">
         <v>1.08</v>
       </c>
-      <c r="I43" s="31">
+      <c r="I43" s="32">
         <v>0.73</v>
       </c>
-      <c r="J43" s="31">
+      <c r="J43" s="32">
         <v>0.68</v>
       </c>
-      <c r="K43" s="31">
+      <c r="K43" s="32">
         <v>0.03</v>
       </c>
-      <c r="L43" s="31">
+      <c r="L43" s="32">
         <v>0.07</v>
       </c>
-      <c r="M43" s="31">
+      <c r="M43" s="32">
         <v>0.08</v>
       </c>
-      <c r="N43" s="31">
+      <c r="N43" s="32">
         <v>0.17</v>
       </c>
-      <c r="O43" s="31">
+      <c r="O43" s="32">
         <v>0.09</v>
       </c>
-      <c r="P43" s="31">
+      <c r="P43" s="32">
         <v>0.05</v>
       </c>
-      <c r="Q43" s="31">
+      <c r="Q43" s="32">
         <v>0.02</v>
       </c>
-      <c r="R43" s="31">
+      <c r="R43" s="32">
         <v>0.03</v>
       </c>
-      <c r="S43" s="31">
+      <c r="S43" s="32">
         <v>0.28</v>
       </c>
-      <c r="T43" s="31">
+      <c r="T43" s="32">
         <v>0.26</v>
       </c>
-      <c r="U43" s="31">
+      <c r="U43" s="32">
         <v>0.14</v>
       </c>
-      <c r="V43" s="31">
+      <c r="V43" s="32">
         <v>0.1</v>
       </c>
-      <c r="W43" s="31">
+      <c r="W43" s="32">
         <v>0.07</v>
       </c>
-      <c r="X43" s="31">
+      <c r="X43" s="32">
         <v>0.04</v>
       </c>
-      <c r="Y43" s="31">
+      <c r="Y43" s="32">
         <v>0.08</v>
       </c>
-      <c r="Z43" s="31">
+      <c r="Z43" s="32">
         <v>0.12</v>
       </c>
-      <c r="AA43" s="31">
+      <c r="AA43" s="32">
         <v>0.06</v>
       </c>
-      <c r="AB43" s="31">
+      <c r="AB43" s="32">
         <v>0.07</v>
       </c>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="28" t="s">
-        <v>456</v>
-      </c>
-      <c r="B44" s="31">
+      <c r="A44" s="29" t="s">
+        <v>457</v>
+      </c>
+      <c r="B44" s="32">
         <v>1.78</v>
       </c>
-      <c r="C44" s="31">
+      <c r="C44" s="32">
         <v>1.7</v>
       </c>
-      <c r="D44" s="31">
+      <c r="D44" s="32">
         <v>1.62</v>
       </c>
-      <c r="E44" s="31">
+      <c r="E44" s="32">
         <v>1.46</v>
       </c>
-      <c r="F44" s="31">
+      <c r="F44" s="32">
         <v>1.07</v>
       </c>
-      <c r="G44" s="31">
+      <c r="G44" s="32">
         <v>0.21</v>
       </c>
-      <c r="H44" s="31">
+      <c r="H44" s="32">
         <v>0.13</v>
       </c>
-      <c r="I44" s="31">
+      <c r="I44" s="32">
         <v>0.09</v>
       </c>
-      <c r="J44" s="31">
+      <c r="J44" s="32">
         <v>0.09</v>
       </c>
-      <c r="K44" s="31">
+      <c r="K44" s="32">
         <v>0.08</v>
       </c>
-      <c r="L44" s="31">
+      <c r="L44" s="32">
         <v>0.09</v>
       </c>
-      <c r="M44" s="31">
+      <c r="M44" s="32">
         <v>0.06</v>
       </c>
-      <c r="N44" s="31">
+      <c r="N44" s="32">
         <v>0.05</v>
       </c>
-      <c r="O44" s="31">
+      <c r="O44" s="32">
         <v>0.09</v>
       </c>
-      <c r="P44" s="31">
+      <c r="P44" s="32">
         <v>0.11</v>
       </c>
-      <c r="Q44" s="31">
+      <c r="Q44" s="32">
         <v>0.12</v>
       </c>
-      <c r="R44" s="31">
+      <c r="R44" s="32">
         <v>0.15</v>
       </c>
-      <c r="S44" s="31">
+      <c r="S44" s="32">
         <v>0.2</v>
       </c>
-      <c r="T44" s="31">
+      <c r="T44" s="32">
         <v>0.14</v>
       </c>
-      <c r="U44" s="31">
+      <c r="U44" s="32">
         <v>0.09</v>
       </c>
-      <c r="V44" s="31">
+      <c r="V44" s="32">
         <v>0.08</v>
       </c>
-      <c r="W44" s="31">
+      <c r="W44" s="32">
         <v>0.07</v>
       </c>
-      <c r="X44" s="31">
+      <c r="X44" s="32">
         <v>0.07</v>
       </c>
-      <c r="Y44" s="32"/>
-      <c r="Z44" s="32"/>
-      <c r="AA44" s="32"/>
-      <c r="AB44" s="32"/>
+      <c r="Y44" s="33"/>
+      <c r="Z44" s="33"/>
+      <c r="AA44" s="33"/>
+      <c r="AB44" s="33"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="26" t="s">
-        <v>457</v>
-      </c>
-      <c r="B45" s="27"/>
-      <c r="C45" s="27"/>
-      <c r="D45" s="27"/>
-      <c r="E45" s="27"/>
-      <c r="F45" s="27"/>
-      <c r="G45" s="27"/>
-      <c r="H45" s="27"/>
-      <c r="I45" s="27"/>
-      <c r="J45" s="27"/>
-      <c r="K45" s="27"/>
-      <c r="L45" s="27"/>
-      <c r="M45" s="27"/>
-      <c r="N45" s="27"/>
-      <c r="O45" s="27"/>
-      <c r="P45" s="27"/>
-      <c r="Q45" s="27"/>
-      <c r="R45" s="27"/>
-      <c r="S45" s="27"/>
-      <c r="T45" s="27"/>
-      <c r="U45" s="27"/>
-      <c r="V45" s="27"/>
-      <c r="W45" s="27"/>
-      <c r="X45" s="27"/>
-      <c r="Y45" s="27"/>
-      <c r="Z45" s="27"/>
-      <c r="AA45" s="27"/>
-      <c r="AB45" s="27"/>
+      <c r="A45" s="27" t="s">
+        <v>458</v>
+      </c>
+      <c r="B45" s="28"/>
+      <c r="C45" s="28"/>
+      <c r="D45" s="28"/>
+      <c r="E45" s="28"/>
+      <c r="F45" s="28"/>
+      <c r="G45" s="28"/>
+      <c r="H45" s="28"/>
+      <c r="I45" s="28"/>
+      <c r="J45" s="28"/>
+      <c r="K45" s="28"/>
+      <c r="L45" s="28"/>
+      <c r="M45" s="28"/>
+      <c r="N45" s="28"/>
+      <c r="O45" s="28"/>
+      <c r="P45" s="28"/>
+      <c r="Q45" s="28"/>
+      <c r="R45" s="28"/>
+      <c r="S45" s="28"/>
+      <c r="T45" s="28"/>
+      <c r="U45" s="28"/>
+      <c r="V45" s="28"/>
+      <c r="W45" s="28"/>
+      <c r="X45" s="28"/>
+      <c r="Y45" s="28"/>
+      <c r="Z45" s="28"/>
+      <c r="AA45" s="28"/>
+      <c r="AB45" s="28"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="28" t="s">
-        <v>458</v>
-      </c>
-      <c r="B46" s="31">
+      <c r="A46" s="29" t="s">
+        <v>459</v>
+      </c>
+      <c r="B46" s="32">
         <v>8.7</v>
       </c>
-      <c r="C46" s="31">
+      <c r="C46" s="32">
         <v>17.23</v>
       </c>
-      <c r="D46" s="29">
+      <c r="D46" s="30">
         <v>100.87</v>
       </c>
-      <c r="E46" s="32"/>
-      <c r="F46" s="31">
+      <c r="E46" s="33"/>
+      <c r="F46" s="32">
         <v>5.54</v>
       </c>
-      <c r="G46" s="31">
+      <c r="G46" s="32">
         <v>4.5</v>
       </c>
-      <c r="H46" s="31">
+      <c r="H46" s="32">
         <v>2.06</v>
       </c>
-      <c r="I46" s="31">
+      <c r="I46" s="32">
         <v>6.8</v>
       </c>
-      <c r="J46" s="32"/>
-      <c r="K46" s="32"/>
-      <c r="L46" s="32"/>
-      <c r="M46" s="32"/>
-      <c r="N46" s="32"/>
-      <c r="O46" s="31">
+      <c r="J46" s="33"/>
+      <c r="K46" s="33"/>
+      <c r="L46" s="33"/>
+      <c r="M46" s="33"/>
+      <c r="N46" s="33"/>
+      <c r="O46" s="32">
         <v>3.14</v>
       </c>
-      <c r="P46" s="32"/>
-      <c r="Q46" s="32"/>
-      <c r="R46" s="32"/>
-      <c r="S46" s="31">
+      <c r="P46" s="33"/>
+      <c r="Q46" s="33"/>
+      <c r="R46" s="33"/>
+      <c r="S46" s="32">
         <v>29.02</v>
       </c>
-      <c r="T46" s="32"/>
-      <c r="U46" s="32"/>
-      <c r="V46" s="32"/>
-      <c r="W46" s="31">
+      <c r="T46" s="33"/>
+      <c r="U46" s="33"/>
+      <c r="V46" s="33"/>
+      <c r="W46" s="32">
         <v>5.29</v>
       </c>
-      <c r="X46" s="32"/>
-      <c r="Y46" s="32"/>
-      <c r="Z46" s="31">
+      <c r="X46" s="33"/>
+      <c r="Y46" s="33"/>
+      <c r="Z46" s="32">
         <v>16.07</v>
       </c>
-      <c r="AA46" s="31">
+      <c r="AA46" s="32">
         <v>2.62</v>
       </c>
-      <c r="AB46" s="32"/>
+      <c r="AB46" s="33"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="28" t="s">
-        <v>459</v>
-      </c>
-      <c r="B47" s="31">
+      <c r="A47" s="29" t="s">
+        <v>460</v>
+      </c>
+      <c r="B47" s="32">
         <v>19.92</v>
       </c>
-      <c r="C47" s="31">
+      <c r="C47" s="32">
         <v>24.22</v>
       </c>
-      <c r="D47" s="31">
+      <c r="D47" s="32">
         <v>12.42</v>
       </c>
-      <c r="E47" s="31">
+      <c r="E47" s="32">
         <v>9.54</v>
       </c>
-      <c r="F47" s="31">
+      <c r="F47" s="32">
         <v>9.28</v>
       </c>
-      <c r="G47" s="32"/>
-      <c r="H47" s="32"/>
-      <c r="I47" s="32"/>
-      <c r="J47" s="32"/>
-      <c r="K47" s="32"/>
-      <c r="L47" s="32"/>
-      <c r="M47" s="32"/>
-      <c r="N47" s="32"/>
-      <c r="O47" s="32"/>
-      <c r="P47" s="32"/>
-      <c r="Q47" s="32"/>
-      <c r="R47" s="32"/>
-      <c r="S47" s="32"/>
-      <c r="T47" s="32"/>
-      <c r="U47" s="32"/>
-      <c r="V47" s="32"/>
-      <c r="W47" s="32"/>
-      <c r="X47" s="32"/>
-      <c r="Y47" s="32"/>
-      <c r="Z47" s="32"/>
-      <c r="AA47" s="32"/>
-      <c r="AB47" s="32"/>
+      <c r="G47" s="33"/>
+      <c r="H47" s="33"/>
+      <c r="I47" s="33"/>
+      <c r="J47" s="33"/>
+      <c r="K47" s="33"/>
+      <c r="L47" s="33"/>
+      <c r="M47" s="33"/>
+      <c r="N47" s="33"/>
+      <c r="O47" s="33"/>
+      <c r="P47" s="33"/>
+      <c r="Q47" s="33"/>
+      <c r="R47" s="33"/>
+      <c r="S47" s="33"/>
+      <c r="T47" s="33"/>
+      <c r="U47" s="33"/>
+      <c r="V47" s="33"/>
+      <c r="W47" s="33"/>
+      <c r="X47" s="33"/>
+      <c r="Y47" s="33"/>
+      <c r="Z47" s="33"/>
+      <c r="AA47" s="33"/>
+      <c r="AB47" s="33"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="26" t="s">
-        <v>460</v>
-      </c>
-      <c r="B48" s="27"/>
-      <c r="C48" s="27"/>
-      <c r="D48" s="27"/>
-      <c r="E48" s="27"/>
-      <c r="F48" s="27"/>
-      <c r="G48" s="27"/>
-      <c r="H48" s="27"/>
-      <c r="I48" s="27"/>
-      <c r="J48" s="27"/>
-      <c r="K48" s="27"/>
-      <c r="L48" s="27"/>
-      <c r="M48" s="27"/>
-      <c r="N48" s="27"/>
-      <c r="O48" s="27"/>
-      <c r="P48" s="27"/>
-      <c r="Q48" s="27"/>
-      <c r="R48" s="27"/>
-      <c r="S48" s="27"/>
-      <c r="T48" s="27"/>
-      <c r="U48" s="27"/>
-      <c r="V48" s="27"/>
-      <c r="W48" s="27"/>
-      <c r="X48" s="27"/>
-      <c r="Y48" s="27"/>
-      <c r="Z48" s="27"/>
-      <c r="AA48" s="27"/>
-      <c r="AB48" s="27"/>
+      <c r="A48" s="27" t="s">
+        <v>461</v>
+      </c>
+      <c r="B48" s="28"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="28"/>
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="28"/>
+      <c r="H48" s="28"/>
+      <c r="I48" s="28"/>
+      <c r="J48" s="28"/>
+      <c r="K48" s="28"/>
+      <c r="L48" s="28"/>
+      <c r="M48" s="28"/>
+      <c r="N48" s="28"/>
+      <c r="O48" s="28"/>
+      <c r="P48" s="28"/>
+      <c r="Q48" s="28"/>
+      <c r="R48" s="28"/>
+      <c r="S48" s="28"/>
+      <c r="T48" s="28"/>
+      <c r="U48" s="28"/>
+      <c r="V48" s="28"/>
+      <c r="W48" s="28"/>
+      <c r="X48" s="28"/>
+      <c r="Y48" s="28"/>
+      <c r="Z48" s="28"/>
+      <c r="AA48" s="28"/>
+      <c r="AB48" s="28"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="28" t="s">
-        <v>461</v>
-      </c>
-      <c r="B49" s="31">
+      <c r="A49" s="29" t="s">
+        <v>462</v>
+      </c>
+      <c r="B49" s="32">
         <v>10.39</v>
       </c>
-      <c r="C49" s="31">
+      <c r="C49" s="32">
         <v>10.59</v>
       </c>
-      <c r="D49" s="31">
+      <c r="D49" s="32">
         <v>15.01</v>
       </c>
-      <c r="E49" s="31">
+      <c r="E49" s="32">
         <v>9.04</v>
       </c>
-      <c r="F49" s="31">
+      <c r="F49" s="32">
         <v>8.65</v>
       </c>
-      <c r="G49" s="31">
+      <c r="G49" s="32">
         <v>3.33</v>
       </c>
-      <c r="H49" s="31">
+      <c r="H49" s="32">
         <v>17.29</v>
       </c>
-      <c r="I49" s="31">
+      <c r="I49" s="32">
         <v>3.21</v>
       </c>
-      <c r="J49" s="31">
+      <c r="J49" s="32">
         <v>3.16</v>
       </c>
-      <c r="K49" s="31">
+      <c r="K49" s="32">
         <v>4.49</v>
       </c>
-      <c r="L49" s="31">
+      <c r="L49" s="32">
         <v>7.93</v>
       </c>
-      <c r="M49" s="32"/>
-      <c r="N49" s="31">
+      <c r="M49" s="33"/>
+      <c r="N49" s="32">
         <v>4.86</v>
       </c>
-      <c r="O49" s="31">
+      <c r="O49" s="32">
         <v>2.4</v>
       </c>
-      <c r="P49" s="32"/>
-      <c r="Q49" s="32"/>
-      <c r="R49" s="31">
+      <c r="P49" s="33"/>
+      <c r="Q49" s="33"/>
+      <c r="R49" s="32">
         <v>1.83</v>
       </c>
-      <c r="S49" s="31">
+      <c r="S49" s="32">
         <v>7.06</v>
       </c>
-      <c r="T49" s="31">
+      <c r="T49" s="32">
         <v>6.0</v>
       </c>
-      <c r="U49" s="31">
+      <c r="U49" s="32">
         <v>3.45</v>
       </c>
-      <c r="V49" s="31">
+      <c r="V49" s="32">
         <v>2.91</v>
       </c>
-      <c r="W49" s="31">
+      <c r="W49" s="32">
         <v>1.46</v>
       </c>
-      <c r="X49" s="31">
+      <c r="X49" s="32">
         <v>0.72</v>
       </c>
-      <c r="Y49" s="31">
+      <c r="Y49" s="32">
         <v>2.54</v>
       </c>
-      <c r="Z49" s="31">
+      <c r="Z49" s="32">
         <v>6.94</v>
       </c>
-      <c r="AA49" s="31">
+      <c r="AA49" s="32">
         <v>1.8</v>
       </c>
-      <c r="AB49" s="31">
+      <c r="AB49" s="32">
         <v>3.08</v>
       </c>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="28" t="s">
-        <v>462</v>
-      </c>
-      <c r="B50" s="31">
+      <c r="A50" s="29" t="s">
+        <v>463</v>
+      </c>
+      <c r="B50" s="32">
         <v>10.23</v>
       </c>
-      <c r="C50" s="31">
+      <c r="C50" s="32">
         <v>9.04</v>
       </c>
-      <c r="D50" s="31">
+      <c r="D50" s="32">
         <v>9.02</v>
       </c>
-      <c r="E50" s="31">
+      <c r="E50" s="32">
         <v>7.21</v>
       </c>
-      <c r="F50" s="31">
+      <c r="F50" s="32">
         <v>5.6</v>
       </c>
-      <c r="G50" s="31">
+      <c r="G50" s="32">
         <v>4.45</v>
       </c>
-      <c r="H50" s="31">
+      <c r="H50" s="32">
         <v>5.35</v>
       </c>
-      <c r="I50" s="32"/>
-      <c r="J50" s="32"/>
-      <c r="K50" s="31">
+      <c r="I50" s="33"/>
+      <c r="J50" s="33"/>
+      <c r="K50" s="32">
         <v>33.73</v>
       </c>
-      <c r="L50" s="32"/>
-      <c r="M50" s="32"/>
-      <c r="N50" s="31">
+      <c r="L50" s="33"/>
+      <c r="M50" s="33"/>
+      <c r="N50" s="32">
         <v>41.4</v>
       </c>
-      <c r="O50" s="31">
+      <c r="O50" s="32">
         <v>12.44</v>
       </c>
-      <c r="P50" s="31">
+      <c r="P50" s="32">
         <v>11.19</v>
       </c>
-      <c r="Q50" s="31">
+      <c r="Q50" s="32">
         <v>6.12</v>
       </c>
-      <c r="R50" s="31">
+      <c r="R50" s="32">
         <v>4.68</v>
       </c>
-      <c r="S50" s="31">
+      <c r="S50" s="32">
         <v>4.76</v>
       </c>
-      <c r="T50" s="31">
+      <c r="T50" s="32">
         <v>3.09</v>
       </c>
-      <c r="U50" s="31">
+      <c r="U50" s="32">
         <v>2.13</v>
       </c>
-      <c r="V50" s="31">
+      <c r="V50" s="32">
         <v>2.27</v>
       </c>
-      <c r="W50" s="31">
+      <c r="W50" s="32">
         <v>2.05</v>
       </c>
-      <c r="X50" s="31">
+      <c r="X50" s="32">
         <v>2.32</v>
       </c>
-      <c r="Y50" s="32"/>
-      <c r="Z50" s="32"/>
-      <c r="AA50" s="32"/>
-      <c r="AB50" s="32"/>
+      <c r="Y50" s="33"/>
+      <c r="Z50" s="33"/>
+      <c r="AA50" s="33"/>
+      <c r="AB50" s="33"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="26" t="s">
-        <v>463</v>
-      </c>
-      <c r="B51" s="27"/>
-      <c r="C51" s="27"/>
-      <c r="D51" s="27"/>
-      <c r="E51" s="27"/>
-      <c r="F51" s="27"/>
-      <c r="G51" s="27"/>
-      <c r="H51" s="27"/>
-      <c r="I51" s="27"/>
-      <c r="J51" s="27"/>
-      <c r="K51" s="27"/>
-      <c r="L51" s="27"/>
-      <c r="M51" s="27"/>
-      <c r="N51" s="27"/>
-      <c r="O51" s="27"/>
-      <c r="P51" s="27"/>
-      <c r="Q51" s="27"/>
-      <c r="R51" s="27"/>
-      <c r="S51" s="27"/>
-      <c r="T51" s="27"/>
-      <c r="U51" s="27"/>
-      <c r="V51" s="27"/>
-      <c r="W51" s="27"/>
-      <c r="X51" s="27"/>
-      <c r="Y51" s="27"/>
-      <c r="Z51" s="27"/>
-      <c r="AA51" s="27"/>
-      <c r="AB51" s="27"/>
+      <c r="A51" s="27" t="s">
+        <v>464</v>
+      </c>
+      <c r="B51" s="28"/>
+      <c r="C51" s="28"/>
+      <c r="D51" s="28"/>
+      <c r="E51" s="28"/>
+      <c r="F51" s="28"/>
+      <c r="G51" s="28"/>
+      <c r="H51" s="28"/>
+      <c r="I51" s="28"/>
+      <c r="J51" s="28"/>
+      <c r="K51" s="28"/>
+      <c r="L51" s="28"/>
+      <c r="M51" s="28"/>
+      <c r="N51" s="28"/>
+      <c r="O51" s="28"/>
+      <c r="P51" s="28"/>
+      <c r="Q51" s="28"/>
+      <c r="R51" s="28"/>
+      <c r="S51" s="28"/>
+      <c r="T51" s="28"/>
+      <c r="U51" s="28"/>
+      <c r="V51" s="28"/>
+      <c r="W51" s="28"/>
+      <c r="X51" s="28"/>
+      <c r="Y51" s="28"/>
+      <c r="Z51" s="28"/>
+      <c r="AA51" s="28"/>
+      <c r="AB51" s="28"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="28" t="s">
-        <v>464</v>
-      </c>
-      <c r="B52" s="31">
+      <c r="A52" s="29" t="s">
+        <v>465</v>
+      </c>
+      <c r="B52" s="32">
         <v>12.26</v>
       </c>
-      <c r="C52" s="31">
+      <c r="C52" s="32">
         <v>11.86</v>
       </c>
-      <c r="D52" s="31">
+      <c r="D52" s="32">
         <v>20.33</v>
       </c>
-      <c r="E52" s="31">
+      <c r="E52" s="32">
         <v>9.62</v>
       </c>
-      <c r="F52" s="31">
+      <c r="F52" s="32">
         <v>9.22</v>
       </c>
-      <c r="G52" s="31">
+      <c r="G52" s="32">
         <v>4.54</v>
       </c>
-      <c r="H52" s="32"/>
-      <c r="I52" s="32"/>
-      <c r="J52" s="32"/>
-      <c r="K52" s="32"/>
-      <c r="L52" s="32"/>
-      <c r="M52" s="32"/>
-      <c r="N52" s="31">
+      <c r="H52" s="33"/>
+      <c r="I52" s="33"/>
+      <c r="J52" s="33"/>
+      <c r="K52" s="33"/>
+      <c r="L52" s="33"/>
+      <c r="M52" s="33"/>
+      <c r="N52" s="32">
         <v>11.15</v>
       </c>
-      <c r="O52" s="31">
+      <c r="O52" s="32">
         <v>6.17</v>
       </c>
-      <c r="P52" s="32"/>
-      <c r="Q52" s="32"/>
-      <c r="R52" s="31">
+      <c r="P52" s="33"/>
+      <c r="Q52" s="33"/>
+      <c r="R52" s="32">
         <v>3.37</v>
       </c>
-      <c r="S52" s="31">
+      <c r="S52" s="32">
         <v>6.5</v>
       </c>
-      <c r="T52" s="31">
+      <c r="T52" s="32">
         <v>5.25</v>
       </c>
-      <c r="U52" s="31">
+      <c r="U52" s="32">
         <v>4.09</v>
       </c>
-      <c r="V52" s="31">
+      <c r="V52" s="32">
         <v>3.79</v>
       </c>
-      <c r="W52" s="31">
+      <c r="W52" s="32">
         <v>65.14</v>
       </c>
-      <c r="X52" s="31">
+      <c r="X52" s="32">
         <v>2.6</v>
       </c>
-      <c r="Y52" s="31">
+      <c r="Y52" s="32">
         <v>7.93</v>
       </c>
-      <c r="Z52" s="32"/>
-      <c r="AA52" s="31">
+      <c r="Z52" s="33"/>
+      <c r="AA52" s="32">
         <v>3.86</v>
       </c>
-      <c r="AB52" s="29">
+      <c r="AB52" s="30">
         <v>187.44</v>
       </c>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="28" t="s">
-        <v>465</v>
-      </c>
-      <c r="B53" s="31">
+      <c r="A53" s="29" t="s">
+        <v>466</v>
+      </c>
+      <c r="B53" s="32">
         <v>11.53</v>
       </c>
-      <c r="C53" s="31">
+      <c r="C53" s="32">
         <v>10.37</v>
       </c>
-      <c r="D53" s="31">
+      <c r="D53" s="32">
         <v>11.1</v>
       </c>
-      <c r="E53" s="31">
+      <c r="E53" s="32">
         <v>11.07</v>
       </c>
-      <c r="F53" s="31">
+      <c r="F53" s="32">
         <v>15.5</v>
       </c>
-      <c r="G53" s="32"/>
-      <c r="H53" s="32"/>
-      <c r="I53" s="32"/>
-      <c r="J53" s="32"/>
-      <c r="K53" s="32"/>
-      <c r="L53" s="32"/>
-      <c r="M53" s="32"/>
-      <c r="N53" s="32"/>
-      <c r="O53" s="32"/>
-      <c r="P53" s="32"/>
-      <c r="Q53" s="31">
+      <c r="G53" s="33"/>
+      <c r="H53" s="33"/>
+      <c r="I53" s="33"/>
+      <c r="J53" s="33"/>
+      <c r="K53" s="33"/>
+      <c r="L53" s="33"/>
+      <c r="M53" s="33"/>
+      <c r="N53" s="33"/>
+      <c r="O53" s="33"/>
+      <c r="P53" s="33"/>
+      <c r="Q53" s="32">
         <v>15.36</v>
       </c>
-      <c r="R53" s="31">
+      <c r="R53" s="32">
         <v>5.11</v>
       </c>
-      <c r="S53" s="31">
+      <c r="S53" s="32">
         <v>5.54</v>
       </c>
-      <c r="T53" s="31">
+      <c r="T53" s="32">
         <v>4.75</v>
       </c>
-      <c r="U53" s="31">
+      <c r="U53" s="32">
         <v>4.75</v>
       </c>
-      <c r="V53" s="31">
+      <c r="V53" s="32">
         <v>8.45</v>
       </c>
-      <c r="W53" s="31">
+      <c r="W53" s="32">
         <v>9.36</v>
       </c>
-      <c r="X53" s="31">
+      <c r="X53" s="32">
         <v>10.05</v>
       </c>
-      <c r="Y53" s="32"/>
-      <c r="Z53" s="32"/>
-      <c r="AA53" s="32"/>
-      <c r="AB53" s="32"/>
+      <c r="Y53" s="33"/>
+      <c r="Z53" s="33"/>
+      <c r="AA53" s="33"/>
+      <c r="AB53" s="33"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="26" t="s">
-        <v>466</v>
-      </c>
-      <c r="B54" s="27"/>
-      <c r="C54" s="27"/>
-      <c r="D54" s="27"/>
-      <c r="E54" s="27"/>
-      <c r="F54" s="27"/>
-      <c r="G54" s="27"/>
-      <c r="H54" s="27"/>
-      <c r="I54" s="27"/>
-      <c r="J54" s="27"/>
-      <c r="K54" s="27"/>
-      <c r="L54" s="27"/>
-      <c r="M54" s="27"/>
-      <c r="N54" s="27"/>
-      <c r="O54" s="27"/>
-      <c r="P54" s="27"/>
-      <c r="Q54" s="27"/>
-      <c r="R54" s="27"/>
-      <c r="S54" s="27"/>
-      <c r="T54" s="27"/>
-      <c r="U54" s="27"/>
-      <c r="V54" s="27"/>
-      <c r="W54" s="27"/>
-      <c r="X54" s="27"/>
-      <c r="Y54" s="27"/>
-      <c r="Z54" s="27"/>
-      <c r="AA54" s="27"/>
-      <c r="AB54" s="27"/>
+      <c r="A54" s="27" t="s">
+        <v>467</v>
+      </c>
+      <c r="B54" s="28"/>
+      <c r="C54" s="28"/>
+      <c r="D54" s="28"/>
+      <c r="E54" s="28"/>
+      <c r="F54" s="28"/>
+      <c r="G54" s="28"/>
+      <c r="H54" s="28"/>
+      <c r="I54" s="28"/>
+      <c r="J54" s="28"/>
+      <c r="K54" s="28"/>
+      <c r="L54" s="28"/>
+      <c r="M54" s="28"/>
+      <c r="N54" s="28"/>
+      <c r="O54" s="28"/>
+      <c r="P54" s="28"/>
+      <c r="Q54" s="28"/>
+      <c r="R54" s="28"/>
+      <c r="S54" s="28"/>
+      <c r="T54" s="28"/>
+      <c r="U54" s="28"/>
+      <c r="V54" s="28"/>
+      <c r="W54" s="28"/>
+      <c r="X54" s="28"/>
+      <c r="Y54" s="28"/>
+      <c r="Z54" s="28"/>
+      <c r="AA54" s="28"/>
+      <c r="AB54" s="28"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="28" t="s">
-        <v>467</v>
-      </c>
-      <c r="B55" s="31">
+      <c r="A55" s="29" t="s">
+        <v>468</v>
+      </c>
+      <c r="B55" s="32">
         <v>9.15</v>
       </c>
-      <c r="C55" s="31">
+      <c r="C55" s="32">
         <v>11.86</v>
       </c>
-      <c r="D55" s="31">
+      <c r="D55" s="32">
         <v>20.33</v>
       </c>
-      <c r="E55" s="31">
+      <c r="E55" s="32">
         <v>9.62</v>
       </c>
-      <c r="F55" s="31">
+      <c r="F55" s="32">
         <v>9.22</v>
       </c>
-      <c r="G55" s="31">
+      <c r="G55" s="32">
         <v>4.54</v>
       </c>
-      <c r="H55" s="32"/>
-      <c r="I55" s="32"/>
-      <c r="J55" s="31">
+      <c r="H55" s="33"/>
+      <c r="I55" s="33"/>
+      <c r="J55" s="32">
         <v>1.85</v>
       </c>
-      <c r="K55" s="31">
+      <c r="K55" s="32">
         <v>0.9</v>
       </c>
-      <c r="L55" s="32"/>
-      <c r="M55" s="32"/>
-      <c r="N55" s="31">
+      <c r="L55" s="33"/>
+      <c r="M55" s="33"/>
+      <c r="N55" s="32">
         <v>11.15</v>
       </c>
-      <c r="O55" s="31">
+      <c r="O55" s="32">
         <v>6.17</v>
       </c>
-      <c r="P55" s="32"/>
-      <c r="Q55" s="32"/>
-      <c r="R55" s="31">
+      <c r="P55" s="33"/>
+      <c r="Q55" s="33"/>
+      <c r="R55" s="32">
         <v>3.37</v>
       </c>
-      <c r="S55" s="31">
+      <c r="S55" s="32">
         <v>8.6</v>
       </c>
-      <c r="T55" s="31">
+      <c r="T55" s="32">
         <v>6.94</v>
       </c>
-      <c r="U55" s="31">
+      <c r="U55" s="32">
         <v>4.09</v>
       </c>
-      <c r="V55" s="31">
+      <c r="V55" s="32">
         <v>3.79</v>
       </c>
-      <c r="W55" s="32"/>
-      <c r="X55" s="31">
+      <c r="W55" s="33"/>
+      <c r="X55" s="32">
         <v>2.6</v>
       </c>
-      <c r="Y55" s="31">
+      <c r="Y55" s="32">
         <v>4.75</v>
       </c>
-      <c r="Z55" s="32"/>
-      <c r="AA55" s="31">
+      <c r="Z55" s="33"/>
+      <c r="AA55" s="32">
         <v>3.86</v>
       </c>
-      <c r="AB55" s="29">
+      <c r="AB55" s="30">
         <v>187.44</v>
       </c>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="28" t="s">
-        <v>468</v>
-      </c>
-      <c r="B56" s="31">
+      <c r="A56" s="29" t="s">
+        <v>469</v>
+      </c>
+      <c r="B56" s="32">
         <v>2.67</v>
       </c>
-      <c r="C56" s="31">
+      <c r="C56" s="32">
         <v>2.47</v>
       </c>
-      <c r="D56" s="31">
+      <c r="D56" s="32">
         <v>1.95</v>
       </c>
-      <c r="E56" s="31">
+      <c r="E56" s="32">
         <v>1.41</v>
       </c>
-      <c r="F56" s="31">
+      <c r="F56" s="32">
         <v>0.76</v>
       </c>
-      <c r="G56" s="31">
+      <c r="G56" s="32">
         <v>0.39</v>
       </c>
-      <c r="H56" s="31">
+      <c r="H56" s="32">
         <v>0.32</v>
       </c>
-      <c r="I56" s="31">
+      <c r="I56" s="32">
         <v>0.29</v>
       </c>
-      <c r="J56" s="31">
+      <c r="J56" s="32">
         <v>0.32</v>
       </c>
-      <c r="K56" s="31">
+      <c r="K56" s="32">
         <v>0.3</v>
       </c>
-      <c r="L56" s="31">
+      <c r="L56" s="32">
         <v>0.3</v>
       </c>
-      <c r="M56" s="31">
+      <c r="M56" s="32">
         <v>0.26</v>
       </c>
-      <c r="N56" s="31">
+      <c r="N56" s="32">
         <v>0.19</v>
       </c>
-      <c r="O56" s="31">
+      <c r="O56" s="32">
         <v>0.34</v>
       </c>
-      <c r="P56" s="31">
+      <c r="P56" s="32">
         <v>0.43</v>
       </c>
-      <c r="Q56" s="31">
+      <c r="Q56" s="32">
         <v>0.46</v>
       </c>
-      <c r="R56" s="31">
+      <c r="R56" s="32">
         <v>0.49</v>
       </c>
-      <c r="S56" s="31">
+      <c r="S56" s="32">
         <v>0.58</v>
       </c>
-      <c r="T56" s="31">
+      <c r="T56" s="32">
         <v>0.43</v>
       </c>
-      <c r="U56" s="31">
+      <c r="U56" s="32">
         <v>0.3</v>
       </c>
-      <c r="V56" s="31">
+      <c r="V56" s="32">
         <v>0.3</v>
       </c>
-      <c r="W56" s="31">
+      <c r="W56" s="32">
         <v>0.29</v>
       </c>
-      <c r="X56" s="31">
+      <c r="X56" s="32">
         <v>0.32</v>
       </c>
-      <c r="Y56" s="32"/>
-      <c r="Z56" s="32"/>
-      <c r="AA56" s="32"/>
-      <c r="AB56" s="32"/>
+      <c r="Y56" s="33"/>
+      <c r="Z56" s="33"/>
+      <c r="AA56" s="33"/>
+      <c r="AB56" s="33"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="26" t="s">
-        <v>469</v>
-      </c>
-      <c r="B57" s="27"/>
-      <c r="C57" s="27"/>
-      <c r="D57" s="27"/>
-      <c r="E57" s="27"/>
-      <c r="F57" s="27"/>
-      <c r="G57" s="27"/>
-      <c r="H57" s="27"/>
-      <c r="I57" s="27"/>
-      <c r="J57" s="27"/>
-      <c r="K57" s="27"/>
-      <c r="L57" s="27"/>
-      <c r="M57" s="27"/>
-      <c r="N57" s="27"/>
-      <c r="O57" s="27"/>
-      <c r="P57" s="27"/>
-      <c r="Q57" s="27"/>
-      <c r="R57" s="27"/>
-      <c r="S57" s="27"/>
-      <c r="T57" s="27"/>
-      <c r="U57" s="27"/>
-      <c r="V57" s="27"/>
-      <c r="W57" s="27"/>
-      <c r="X57" s="27"/>
-      <c r="Y57" s="27"/>
-      <c r="Z57" s="27"/>
-      <c r="AA57" s="27"/>
-      <c r="AB57" s="27"/>
+      <c r="A57" s="27" t="s">
+        <v>470</v>
+      </c>
+      <c r="B57" s="28"/>
+      <c r="C57" s="28"/>
+      <c r="D57" s="28"/>
+      <c r="E57" s="28"/>
+      <c r="F57" s="28"/>
+      <c r="G57" s="28"/>
+      <c r="H57" s="28"/>
+      <c r="I57" s="28"/>
+      <c r="J57" s="28"/>
+      <c r="K57" s="28"/>
+      <c r="L57" s="28"/>
+      <c r="M57" s="28"/>
+      <c r="N57" s="28"/>
+      <c r="O57" s="28"/>
+      <c r="P57" s="28"/>
+      <c r="Q57" s="28"/>
+      <c r="R57" s="28"/>
+      <c r="S57" s="28"/>
+      <c r="T57" s="28"/>
+      <c r="U57" s="28"/>
+      <c r="V57" s="28"/>
+      <c r="W57" s="28"/>
+      <c r="X57" s="28"/>
+      <c r="Y57" s="28"/>
+      <c r="Z57" s="28"/>
+      <c r="AA57" s="28"/>
+      <c r="AB57" s="28"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="28" t="s">
-        <v>470</v>
-      </c>
-      <c r="B58" s="31">
+      <c r="A58" s="29" t="s">
+        <v>471</v>
+      </c>
+      <c r="B58" s="32">
         <v>2.39</v>
       </c>
-      <c r="C58" s="31">
+      <c r="C58" s="32">
         <v>0.07</v>
       </c>
-      <c r="D58" s="30">
+      <c r="D58" s="31">
         <v>-0.29</v>
       </c>
-      <c r="E58" s="31">
+      <c r="E58" s="32">
         <v>0.16</v>
       </c>
-      <c r="F58" s="31">
+      <c r="F58" s="32">
         <v>0.21</v>
       </c>
-      <c r="G58" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="H58" s="32"/>
-      <c r="I58" s="32"/>
-      <c r="J58" s="32"/>
-      <c r="K58" s="32"/>
-      <c r="L58" s="32"/>
-      <c r="M58" s="32"/>
-      <c r="N58" s="30">
+      <c r="G58" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="H58" s="33"/>
+      <c r="I58" s="33"/>
+      <c r="J58" s="33"/>
+      <c r="K58" s="33"/>
+      <c r="L58" s="33"/>
+      <c r="M58" s="33"/>
+      <c r="N58" s="31">
         <v>-0.58</v>
       </c>
-      <c r="O58" s="31">
+      <c r="O58" s="32">
         <v>0.05</v>
       </c>
-      <c r="P58" s="32"/>
-      <c r="Q58" s="32"/>
-      <c r="R58" s="30">
+      <c r="P58" s="33"/>
+      <c r="Q58" s="33"/>
+      <c r="R58" s="31">
         <v>-0.05</v>
       </c>
-      <c r="S58" s="31">
+      <c r="S58" s="32">
         <v>0.54</v>
       </c>
-      <c r="T58" s="31">
+      <c r="T58" s="32">
         <v>0.07</v>
       </c>
-      <c r="U58" s="31">
+      <c r="U58" s="32">
         <v>0.08</v>
       </c>
-      <c r="V58" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="W58" s="30">
+      <c r="V58" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="W58" s="31">
         <v>-0.69</v>
       </c>
-      <c r="X58" s="31">
+      <c r="X58" s="32">
         <v>0.07</v>
       </c>
-      <c r="Y58" s="31">
+      <c r="Y58" s="32">
         <v>0.03</v>
       </c>
-      <c r="Z58" s="32"/>
-      <c r="AA58" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="AB58" s="32"/>
+      <c r="Z58" s="33"/>
+      <c r="AA58" s="33">
+        <v>0.0</v>
+      </c>
+      <c r="AB58" s="33"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="28" t="s">
-        <v>471</v>
-      </c>
-      <c r="B59" s="31">
+      <c r="A59" s="29" t="s">
+        <v>472</v>
+      </c>
+      <c r="B59" s="32">
         <v>0.91</v>
       </c>
-      <c r="C59" s="32"/>
-      <c r="D59" s="32"/>
-      <c r="E59" s="32"/>
-      <c r="F59" s="32"/>
-      <c r="G59" s="32"/>
-      <c r="H59" s="32"/>
-      <c r="I59" s="32"/>
-      <c r="J59" s="32"/>
-      <c r="K59" s="32"/>
-      <c r="L59" s="32"/>
-      <c r="M59" s="32"/>
-      <c r="N59" s="32"/>
-      <c r="O59" s="32"/>
-      <c r="P59" s="32"/>
-      <c r="Q59" s="32"/>
-      <c r="R59" s="31">
+      <c r="C59" s="33"/>
+      <c r="D59" s="33"/>
+      <c r="E59" s="33"/>
+      <c r="F59" s="33"/>
+      <c r="G59" s="33"/>
+      <c r="H59" s="33"/>
+      <c r="I59" s="33"/>
+      <c r="J59" s="33"/>
+      <c r="K59" s="33"/>
+      <c r="L59" s="33"/>
+      <c r="M59" s="33"/>
+      <c r="N59" s="33"/>
+      <c r="O59" s="33"/>
+      <c r="P59" s="33"/>
+      <c r="Q59" s="33"/>
+      <c r="R59" s="32">
         <v>0.05</v>
       </c>
-      <c r="S59" s="31">
+      <c r="S59" s="32">
         <v>0.14</v>
       </c>
-      <c r="T59" s="31">
+      <c r="T59" s="32">
         <v>0.11</v>
       </c>
-      <c r="U59" s="32"/>
-      <c r="V59" s="31">
+      <c r="U59" s="33"/>
+      <c r="V59" s="32">
         <v>1.19</v>
       </c>
-      <c r="W59" s="31">
+      <c r="W59" s="32">
         <v>0.64</v>
       </c>
-      <c r="X59" s="32"/>
-      <c r="Y59" s="32"/>
-      <c r="Z59" s="32"/>
-      <c r="AA59" s="32"/>
-      <c r="AB59" s="32"/>
+      <c r="X59" s="33"/>
+      <c r="Y59" s="33"/>
+      <c r="Z59" s="33"/>
+      <c r="AA59" s="33"/>
+      <c r="AB59" s="33"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="26" t="s">
-        <v>472</v>
-      </c>
-      <c r="B60" s="27"/>
-      <c r="C60" s="27"/>
-      <c r="D60" s="27"/>
-      <c r="E60" s="27"/>
-      <c r="F60" s="27"/>
-      <c r="G60" s="27"/>
-      <c r="H60" s="27"/>
-      <c r="I60" s="27"/>
-      <c r="J60" s="27"/>
-      <c r="K60" s="27"/>
-      <c r="L60" s="27"/>
-      <c r="M60" s="27"/>
-      <c r="N60" s="27"/>
-      <c r="O60" s="27"/>
-      <c r="P60" s="27"/>
-      <c r="Q60" s="27"/>
-      <c r="R60" s="27"/>
-      <c r="S60" s="27"/>
-      <c r="T60" s="27"/>
-      <c r="U60" s="27"/>
-      <c r="V60" s="27"/>
-      <c r="W60" s="27"/>
-      <c r="X60" s="27"/>
-      <c r="Y60" s="27"/>
-      <c r="Z60" s="27"/>
-      <c r="AA60" s="27"/>
-      <c r="AB60" s="27"/>
+      <c r="A60" s="27" t="s">
+        <v>473</v>
+      </c>
+      <c r="B60" s="28"/>
+      <c r="C60" s="28"/>
+      <c r="D60" s="28"/>
+      <c r="E60" s="28"/>
+      <c r="F60" s="28"/>
+      <c r="G60" s="28"/>
+      <c r="H60" s="28"/>
+      <c r="I60" s="28"/>
+      <c r="J60" s="28"/>
+      <c r="K60" s="28"/>
+      <c r="L60" s="28"/>
+      <c r="M60" s="28"/>
+      <c r="N60" s="28"/>
+      <c r="O60" s="28"/>
+      <c r="P60" s="28"/>
+      <c r="Q60" s="28"/>
+      <c r="R60" s="28"/>
+      <c r="S60" s="28"/>
+      <c r="T60" s="28"/>
+      <c r="U60" s="28"/>
+      <c r="V60" s="28"/>
+      <c r="W60" s="28"/>
+      <c r="X60" s="28"/>
+      <c r="Y60" s="28"/>
+      <c r="Z60" s="28"/>
+      <c r="AA60" s="28"/>
+      <c r="AB60" s="28"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="28" t="s">
-        <v>473</v>
-      </c>
-      <c r="B61" s="31">
+      <c r="A61" s="29" t="s">
+        <v>474</v>
+      </c>
+      <c r="B61" s="32">
         <v>1.54</v>
       </c>
-      <c r="C61" s="31">
+      <c r="C61" s="32">
         <v>1.45</v>
       </c>
-      <c r="D61" s="31">
+      <c r="D61" s="32">
         <v>1.28</v>
       </c>
-      <c r="E61" s="31">
+      <c r="E61" s="32">
         <v>1.9</v>
       </c>
-      <c r="F61" s="31">
+      <c r="F61" s="32">
         <v>0.82</v>
       </c>
-      <c r="G61" s="30">
+      <c r="G61" s="31">
         <v>-0.11</v>
       </c>
-      <c r="H61" s="31">
+      <c r="H61" s="32">
         <v>1.5</v>
       </c>
-      <c r="I61" s="31">
+      <c r="I61" s="32">
         <v>1.82</v>
       </c>
-      <c r="J61" s="31">
+      <c r="J61" s="32">
         <v>2.85</v>
       </c>
-      <c r="K61" s="31">
+      <c r="K61" s="32">
         <v>0.14</v>
       </c>
-      <c r="L61" s="31">
+      <c r="L61" s="32">
         <v>0.18</v>
       </c>
-      <c r="M61" s="31">
+      <c r="M61" s="32">
         <v>0.11</v>
       </c>
-      <c r="N61" s="31">
+      <c r="N61" s="32">
         <v>0.1</v>
       </c>
-      <c r="O61" s="31">
+      <c r="O61" s="32">
         <v>0.28</v>
       </c>
-      <c r="P61" s="31">
+      <c r="P61" s="32">
         <v>0.27</v>
       </c>
-      <c r="Q61" s="31">
+      <c r="Q61" s="32">
         <v>0.25</v>
       </c>
-      <c r="R61" s="31">
+      <c r="R61" s="32">
         <v>0.15</v>
       </c>
-      <c r="S61" s="31">
+      <c r="S61" s="32">
         <v>0.4</v>
       </c>
-      <c r="T61" s="31">
+      <c r="T61" s="32">
         <v>0.27</v>
       </c>
-      <c r="U61" s="31">
+      <c r="U61" s="32">
         <v>0.12</v>
       </c>
-      <c r="V61" s="31">
+      <c r="V61" s="32">
         <v>0.19</v>
       </c>
-      <c r="W61" s="31">
+      <c r="W61" s="32">
         <v>0.09</v>
       </c>
-      <c r="X61" s="31">
+      <c r="X61" s="32">
         <v>0.06</v>
       </c>
-      <c r="Y61" s="31">
+      <c r="Y61" s="32">
         <v>0.26</v>
       </c>
-      <c r="Z61" s="31">
+      <c r="Z61" s="32">
         <v>0.11</v>
       </c>
-      <c r="AA61" s="31">
+      <c r="AA61" s="32">
         <v>0.15</v>
       </c>
-      <c r="AB61" s="31">
+      <c r="AB61" s="32">
         <v>0.23</v>
       </c>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="28" t="s">
-        <v>474</v>
-      </c>
-      <c r="B62" s="31">
+      <c r="A62" s="29" t="s">
+        <v>475</v>
+      </c>
+      <c r="B62" s="32">
         <v>1.44</v>
       </c>
-      <c r="C62" s="31">
+      <c r="C62" s="32">
         <v>1.21</v>
       </c>
-      <c r="D62" s="31">
+      <c r="D62" s="32">
         <v>1.17</v>
       </c>
-      <c r="E62" s="31">
+      <c r="E62" s="32">
         <v>1.23</v>
       </c>
-      <c r="F62" s="31">
+      <c r="F62" s="32">
         <v>1.24</v>
       </c>
-      <c r="G62" s="31">
+      <c r="G62" s="32">
         <v>0.43</v>
       </c>
-      <c r="H62" s="31">
+      <c r="H62" s="32">
         <v>0.35</v>
       </c>
-      <c r="I62" s="31">
+      <c r="I62" s="32">
         <v>0.25</v>
       </c>
-      <c r="J62" s="31">
+      <c r="J62" s="32">
         <v>0.18</v>
       </c>
-      <c r="K62" s="31">
+      <c r="K62" s="32">
         <v>0.16</v>
       </c>
-      <c r="L62" s="31">
+      <c r="L62" s="32">
         <v>0.19</v>
       </c>
-      <c r="M62" s="31">
+      <c r="M62" s="32">
         <v>0.21</v>
       </c>
-      <c r="N62" s="31">
+      <c r="N62" s="32">
         <v>0.21</v>
       </c>
-      <c r="O62" s="31">
+      <c r="O62" s="32">
         <v>0.26</v>
       </c>
-      <c r="P62" s="31">
+      <c r="P62" s="32">
         <v>0.25</v>
       </c>
-      <c r="Q62" s="31">
+      <c r="Q62" s="32">
         <v>0.24</v>
       </c>
-      <c r="R62" s="31">
+      <c r="R62" s="32">
         <v>0.23</v>
       </c>
-      <c r="S62" s="31">
+      <c r="S62" s="32">
         <v>0.27</v>
       </c>
-      <c r="T62" s="31">
+      <c r="T62" s="32">
         <v>0.17</v>
       </c>
-      <c r="U62" s="31">
+      <c r="U62" s="32">
         <v>0.13</v>
       </c>
-      <c r="V62" s="31">
+      <c r="V62" s="32">
         <v>0.13</v>
       </c>
-      <c r="W62" s="31">
+      <c r="W62" s="32">
         <v>0.12</v>
       </c>
-      <c r="X62" s="31">
+      <c r="X62" s="32">
         <v>0.14</v>
       </c>
-      <c r="Y62" s="32"/>
-      <c r="Z62" s="32"/>
-      <c r="AA62" s="32"/>
-      <c r="AB62" s="32"/>
+      <c r="Y62" s="33"/>
+      <c r="Z62" s="33"/>
+      <c r="AA62" s="33"/>
+      <c r="AB62" s="33"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="26" t="s">
-        <v>475</v>
-      </c>
-      <c r="B63" s="27"/>
-      <c r="C63" s="27"/>
-      <c r="D63" s="27"/>
-      <c r="E63" s="27"/>
-      <c r="F63" s="27"/>
-      <c r="G63" s="27"/>
-      <c r="H63" s="27"/>
-      <c r="I63" s="27"/>
-      <c r="J63" s="27"/>
-      <c r="K63" s="27"/>
-      <c r="L63" s="27"/>
-      <c r="M63" s="27"/>
-      <c r="N63" s="27"/>
-      <c r="O63" s="27"/>
-      <c r="P63" s="27"/>
-      <c r="Q63" s="27"/>
-      <c r="R63" s="27"/>
-      <c r="S63" s="27"/>
-      <c r="T63" s="27"/>
-      <c r="U63" s="27"/>
-      <c r="V63" s="27"/>
-      <c r="W63" s="27"/>
-      <c r="X63" s="27"/>
-      <c r="Y63" s="27"/>
-      <c r="Z63" s="27"/>
-      <c r="AA63" s="27"/>
-      <c r="AB63" s="27"/>
+      <c r="A63" s="27" t="s">
+        <v>476</v>
+      </c>
+      <c r="B63" s="28"/>
+      <c r="C63" s="28"/>
+      <c r="D63" s="28"/>
+      <c r="E63" s="28"/>
+      <c r="F63" s="28"/>
+      <c r="G63" s="28"/>
+      <c r="H63" s="28"/>
+      <c r="I63" s="28"/>
+      <c r="J63" s="28"/>
+      <c r="K63" s="28"/>
+      <c r="L63" s="28"/>
+      <c r="M63" s="28"/>
+      <c r="N63" s="28"/>
+      <c r="O63" s="28"/>
+      <c r="P63" s="28"/>
+      <c r="Q63" s="28"/>
+      <c r="R63" s="28"/>
+      <c r="S63" s="28"/>
+      <c r="T63" s="28"/>
+      <c r="U63" s="28"/>
+      <c r="V63" s="28"/>
+      <c r="W63" s="28"/>
+      <c r="X63" s="28"/>
+      <c r="Y63" s="28"/>
+      <c r="Z63" s="28"/>
+      <c r="AA63" s="28"/>
+      <c r="AB63" s="28"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="28" t="s">
-        <v>476</v>
-      </c>
-      <c r="B64" s="31">
+      <c r="A64" s="29" t="s">
+        <v>477</v>
+      </c>
+      <c r="B64" s="32">
         <v>10.4</v>
       </c>
-      <c r="C64" s="31">
+      <c r="C64" s="32">
         <v>7.69</v>
       </c>
-      <c r="D64" s="31">
+      <c r="D64" s="32">
         <v>7.35</v>
       </c>
-      <c r="E64" s="31">
+      <c r="E64" s="32">
         <v>6.53</v>
       </c>
-      <c r="F64" s="31">
+      <c r="F64" s="32">
         <v>3.82</v>
       </c>
-      <c r="G64" s="30">
+      <c r="G64" s="31">
         <v>-0.58</v>
       </c>
-      <c r="H64" s="31">
+      <c r="H64" s="32">
         <v>2.08</v>
       </c>
-      <c r="I64" s="31">
+      <c r="I64" s="32">
         <v>7.89</v>
       </c>
-      <c r="J64" s="31">
+      <c r="J64" s="32">
         <v>4.65</v>
       </c>
-      <c r="K64" s="31">
+      <c r="K64" s="32">
         <v>3.07</v>
       </c>
-      <c r="L64" s="31">
+      <c r="L64" s="32">
         <v>4.73</v>
       </c>
-      <c r="M64" s="32"/>
-      <c r="N64" s="31">
+      <c r="M64" s="33"/>
+      <c r="N64" s="32">
         <v>2.34</v>
       </c>
-      <c r="O64" s="31">
+      <c r="O64" s="32">
         <v>4.57</v>
       </c>
-      <c r="P64" s="32"/>
-      <c r="Q64" s="32"/>
-      <c r="R64" s="31">
+      <c r="P64" s="33"/>
+      <c r="Q64" s="33"/>
+      <c r="R64" s="32">
         <v>4.95</v>
       </c>
-      <c r="S64" s="31">
+      <c r="S64" s="32">
         <v>7.17</v>
       </c>
-      <c r="T64" s="31">
+      <c r="T64" s="32">
         <v>4.36</v>
       </c>
-      <c r="U64" s="31">
+      <c r="U64" s="32">
         <v>2.09</v>
       </c>
-      <c r="V64" s="31">
+      <c r="V64" s="32">
         <v>3.44</v>
       </c>
-      <c r="W64" s="31">
+      <c r="W64" s="32">
         <v>2.26</v>
       </c>
-      <c r="X64" s="31">
+      <c r="X64" s="32">
         <v>0.99</v>
       </c>
-      <c r="Y64" s="31">
+      <c r="Y64" s="32">
         <v>6.64</v>
       </c>
-      <c r="Z64" s="31">
+      <c r="Z64" s="32">
         <v>4.63</v>
       </c>
-      <c r="AA64" s="31">
+      <c r="AA64" s="32">
         <v>2.54</v>
       </c>
-      <c r="AB64" s="31">
+      <c r="AB64" s="32">
         <v>6.23</v>
       </c>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="28" t="s">
-        <v>477</v>
-      </c>
-      <c r="B65" s="31">
+      <c r="A65" s="29" t="s">
+        <v>478</v>
+      </c>
+      <c r="B65" s="32">
         <v>7.21</v>
       </c>
-      <c r="C65" s="31">
+      <c r="C65" s="32">
         <v>5.67</v>
       </c>
-      <c r="D65" s="31">
+      <c r="D65" s="32">
         <v>4.07</v>
       </c>
-      <c r="E65" s="31">
+      <c r="E65" s="32">
         <v>4.0</v>
       </c>
-      <c r="F65" s="31">
+      <c r="F65" s="32">
         <v>3.4</v>
       </c>
-      <c r="G65" s="31">
+      <c r="G65" s="32">
         <v>3.25</v>
       </c>
-      <c r="H65" s="31">
+      <c r="H65" s="32">
         <v>3.82</v>
       </c>
-      <c r="I65" s="31">
+      <c r="I65" s="32">
         <v>7.77</v>
       </c>
-      <c r="J65" s="31">
+      <c r="J65" s="32">
         <v>6.11</v>
       </c>
-      <c r="K65" s="31">
+      <c r="K65" s="32">
         <v>5.95</v>
       </c>
-      <c r="L65" s="31">
+      <c r="L65" s="32">
         <v>12.59</v>
       </c>
-      <c r="M65" s="29">
+      <c r="M65" s="30">
         <v>121.87</v>
       </c>
-      <c r="N65" s="31">
+      <c r="N65" s="32">
         <v>12.04</v>
       </c>
-      <c r="O65" s="31">
+      <c r="O65" s="32">
         <v>12.9</v>
       </c>
-      <c r="P65" s="31">
+      <c r="P65" s="32">
         <v>14.62</v>
       </c>
-      <c r="Q65" s="31">
+      <c r="Q65" s="32">
         <v>9.14</v>
       </c>
-      <c r="R65" s="31">
+      <c r="R65" s="32">
         <v>4.93</v>
       </c>
-      <c r="S65" s="31">
+      <c r="S65" s="32">
         <v>4.73</v>
       </c>
-      <c r="T65" s="31">
+      <c r="T65" s="32">
         <v>2.95</v>
       </c>
-      <c r="U65" s="31">
+      <c r="U65" s="32">
         <v>2.52</v>
       </c>
-      <c r="V65" s="31">
+      <c r="V65" s="32">
         <v>2.86</v>
       </c>
-      <c r="W65" s="31">
+      <c r="W65" s="32">
         <v>2.59</v>
       </c>
-      <c r="X65" s="31">
+      <c r="X65" s="32">
         <v>3.11</v>
       </c>
-      <c r="Y65" s="32"/>
-      <c r="Z65" s="32"/>
-      <c r="AA65" s="32"/>
-      <c r="AB65" s="32"/>
+      <c r="Y65" s="33"/>
+      <c r="Z65" s="33"/>
+      <c r="AA65" s="33"/>
+      <c r="AB65" s="33"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="26" t="s">
-        <v>478</v>
-      </c>
-      <c r="B66" s="27"/>
-      <c r="C66" s="27"/>
-      <c r="D66" s="27"/>
-      <c r="E66" s="27"/>
-      <c r="F66" s="27"/>
-      <c r="G66" s="27"/>
-      <c r="H66" s="27"/>
-      <c r="I66" s="27"/>
-      <c r="J66" s="27"/>
-      <c r="K66" s="27"/>
-      <c r="L66" s="27"/>
-      <c r="M66" s="27"/>
-      <c r="N66" s="27"/>
-      <c r="O66" s="27"/>
-      <c r="P66" s="27"/>
-      <c r="Q66" s="27"/>
-      <c r="R66" s="27"/>
-      <c r="S66" s="27"/>
-      <c r="T66" s="27"/>
-      <c r="U66" s="27"/>
-      <c r="V66" s="27"/>
-      <c r="W66" s="27"/>
-      <c r="X66" s="27"/>
-      <c r="Y66" s="27"/>
-      <c r="Z66" s="27"/>
-      <c r="AA66" s="27"/>
-      <c r="AB66" s="27"/>
+      <c r="A66" s="27" t="s">
+        <v>479</v>
+      </c>
+      <c r="B66" s="28"/>
+      <c r="C66" s="28"/>
+      <c r="D66" s="28"/>
+      <c r="E66" s="28"/>
+      <c r="F66" s="28"/>
+      <c r="G66" s="28"/>
+      <c r="H66" s="28"/>
+      <c r="I66" s="28"/>
+      <c r="J66" s="28"/>
+      <c r="K66" s="28"/>
+      <c r="L66" s="28"/>
+      <c r="M66" s="28"/>
+      <c r="N66" s="28"/>
+      <c r="O66" s="28"/>
+      <c r="P66" s="28"/>
+      <c r="Q66" s="28"/>
+      <c r="R66" s="28"/>
+      <c r="S66" s="28"/>
+      <c r="T66" s="28"/>
+      <c r="U66" s="28"/>
+      <c r="V66" s="28"/>
+      <c r="W66" s="28"/>
+      <c r="X66" s="28"/>
+      <c r="Y66" s="28"/>
+      <c r="Z66" s="28"/>
+      <c r="AA66" s="28"/>
+      <c r="AB66" s="28"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="28" t="s">
-        <v>479</v>
-      </c>
-      <c r="B67" s="31">
+      <c r="A67" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="B67" s="32">
         <v>6.78</v>
       </c>
-      <c r="C67" s="31">
+      <c r="C67" s="32">
         <v>11.12</v>
       </c>
-      <c r="D67" s="31">
+      <c r="D67" s="32">
         <v>17.16</v>
       </c>
-      <c r="E67" s="32"/>
-      <c r="F67" s="31">
+      <c r="E67" s="33"/>
+      <c r="F67" s="32">
         <v>2.33</v>
       </c>
-      <c r="G67" s="30">
+      <c r="G67" s="31">
         <v>-0.46</v>
       </c>
-      <c r="H67" s="31">
+      <c r="H67" s="32">
         <v>2.7</v>
       </c>
-      <c r="I67" s="31">
+      <c r="I67" s="32">
         <v>14.54</v>
       </c>
-      <c r="J67" s="32"/>
-      <c r="K67" s="32"/>
-      <c r="L67" s="32"/>
-      <c r="M67" s="32"/>
-      <c r="N67" s="32"/>
-      <c r="O67" s="31">
+      <c r="J67" s="33"/>
+      <c r="K67" s="33"/>
+      <c r="L67" s="33"/>
+      <c r="M67" s="33"/>
+      <c r="N67" s="33"/>
+      <c r="O67" s="32">
         <v>8.12</v>
       </c>
-      <c r="P67" s="31">
+      <c r="P67" s="32">
         <v>36.28</v>
       </c>
-      <c r="Q67" s="32"/>
-      <c r="R67" s="32"/>
-      <c r="S67" s="31">
+      <c r="Q67" s="33"/>
+      <c r="R67" s="33"/>
+      <c r="S67" s="32">
         <v>41.77</v>
       </c>
-      <c r="T67" s="29">
+      <c r="T67" s="30">
         <v>463.99</v>
       </c>
-      <c r="U67" s="32"/>
-      <c r="V67" s="31">
+      <c r="U67" s="33"/>
+      <c r="V67" s="32">
         <v>20.61</v>
       </c>
-      <c r="W67" s="31">
+      <c r="W67" s="32">
         <v>5.48</v>
       </c>
-      <c r="X67" s="32"/>
-      <c r="Y67" s="31">
+      <c r="X67" s="33"/>
+      <c r="Y67" s="32">
         <v>2.77</v>
       </c>
-      <c r="Z67" s="31">
+      <c r="Z67" s="32">
         <v>3.31</v>
       </c>
-      <c r="AA67" s="31">
+      <c r="AA67" s="32">
         <v>3.73</v>
       </c>
-      <c r="AB67" s="32"/>
+      <c r="AB67" s="33"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="28" t="s">
-        <v>480</v>
-      </c>
-      <c r="B68" s="31">
+      <c r="A68" s="29" t="s">
+        <v>481</v>
+      </c>
+      <c r="B68" s="32">
         <v>11.01</v>
       </c>
-      <c r="C68" s="31">
+      <c r="C68" s="32">
         <v>10.56</v>
       </c>
-      <c r="D68" s="31">
+      <c r="D68" s="32">
         <v>7.03</v>
       </c>
-      <c r="E68" s="31">
+      <c r="E68" s="32">
         <v>6.7</v>
       </c>
-      <c r="F68" s="31">
+      <c r="F68" s="32">
         <v>7.36</v>
       </c>
-      <c r="G68" s="31">
+      <c r="G68" s="32">
         <v>54.39</v>
       </c>
-      <c r="H68" s="32"/>
-      <c r="I68" s="32"/>
-      <c r="J68" s="32"/>
-      <c r="K68" s="32"/>
-      <c r="L68" s="32"/>
-      <c r="M68" s="32"/>
-      <c r="N68" s="32"/>
-      <c r="O68" s="32"/>
-      <c r="P68" s="32"/>
-      <c r="Q68" s="32"/>
-      <c r="R68" s="32"/>
-      <c r="S68" s="32"/>
-      <c r="T68" s="32"/>
-      <c r="U68" s="32"/>
-      <c r="V68" s="31">
+      <c r="H68" s="33"/>
+      <c r="I68" s="33"/>
+      <c r="J68" s="33"/>
+      <c r="K68" s="33"/>
+      <c r="L68" s="33"/>
+      <c r="M68" s="33"/>
+      <c r="N68" s="33"/>
+      <c r="O68" s="33"/>
+      <c r="P68" s="33"/>
+      <c r="Q68" s="33"/>
+      <c r="R68" s="33"/>
+      <c r="S68" s="33"/>
+      <c r="T68" s="33"/>
+      <c r="U68" s="33"/>
+      <c r="V68" s="32">
         <v>6.9</v>
       </c>
-      <c r="W68" s="31">
+      <c r="W68" s="32">
         <v>4.65</v>
       </c>
-      <c r="X68" s="31">
+      <c r="X68" s="32">
         <v>6.17</v>
       </c>
-      <c r="Y68" s="32"/>
-      <c r="Z68" s="32"/>
-      <c r="AA68" s="32"/>
-      <c r="AB68" s="32"/>
+      <c r="Y68" s="33"/>
+      <c r="Z68" s="33"/>
+      <c r="AA68" s="33"/>
+      <c r="AB68" s="33"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="26" t="s">
-        <v>481</v>
-      </c>
-      <c r="B69" s="27"/>
-      <c r="C69" s="27"/>
-      <c r="D69" s="27"/>
-      <c r="E69" s="27"/>
-      <c r="F69" s="27"/>
-      <c r="G69" s="27"/>
-      <c r="H69" s="27"/>
-      <c r="I69" s="27"/>
-      <c r="J69" s="27"/>
-      <c r="K69" s="27"/>
-      <c r="L69" s="27"/>
-      <c r="M69" s="27"/>
-      <c r="N69" s="27"/>
-      <c r="O69" s="27"/>
-      <c r="P69" s="27"/>
-      <c r="Q69" s="27"/>
-      <c r="R69" s="27"/>
-      <c r="S69" s="27"/>
-      <c r="T69" s="27"/>
-      <c r="U69" s="27"/>
-      <c r="V69" s="27"/>
-      <c r="W69" s="27"/>
-      <c r="X69" s="27"/>
-      <c r="Y69" s="27"/>
-      <c r="Z69" s="27"/>
-      <c r="AA69" s="27"/>
-      <c r="AB69" s="27"/>
+      <c r="A69" s="27" t="s">
+        <v>482</v>
+      </c>
+      <c r="B69" s="28"/>
+      <c r="C69" s="28"/>
+      <c r="D69" s="28"/>
+      <c r="E69" s="28"/>
+      <c r="F69" s="28"/>
+      <c r="G69" s="28"/>
+      <c r="H69" s="28"/>
+      <c r="I69" s="28"/>
+      <c r="J69" s="28"/>
+      <c r="K69" s="28"/>
+      <c r="L69" s="28"/>
+      <c r="M69" s="28"/>
+      <c r="N69" s="28"/>
+      <c r="O69" s="28"/>
+      <c r="P69" s="28"/>
+      <c r="Q69" s="28"/>
+      <c r="R69" s="28"/>
+      <c r="S69" s="28"/>
+      <c r="T69" s="28"/>
+      <c r="U69" s="28"/>
+      <c r="V69" s="28"/>
+      <c r="W69" s="28"/>
+      <c r="X69" s="28"/>
+      <c r="Y69" s="28"/>
+      <c r="Z69" s="28"/>
+      <c r="AA69" s="28"/>
+      <c r="AB69" s="28"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="28" t="s">
-        <v>482</v>
-      </c>
-      <c r="B70" s="31">
+      <c r="A70" s="29" t="s">
+        <v>483</v>
+      </c>
+      <c r="B70" s="32">
         <v>8.24</v>
       </c>
-      <c r="C70" s="31">
+      <c r="C70" s="32">
         <v>14.94</v>
       </c>
-      <c r="D70" s="31">
+      <c r="D70" s="32">
         <v>77.04</v>
       </c>
-      <c r="E70" s="32"/>
-      <c r="F70" s="31">
+      <c r="E70" s="33"/>
+      <c r="F70" s="32">
         <v>2.58</v>
       </c>
-      <c r="G70" s="30">
+      <c r="G70" s="31">
         <v>-0.59</v>
       </c>
-      <c r="H70" s="31">
+      <c r="H70" s="32">
         <v>2.88</v>
       </c>
-      <c r="I70" s="31">
+      <c r="I70" s="32">
         <v>16.95</v>
       </c>
-      <c r="J70" s="32"/>
-      <c r="K70" s="32"/>
-      <c r="L70" s="32"/>
-      <c r="M70" s="32"/>
-      <c r="N70" s="32"/>
-      <c r="O70" s="31">
+      <c r="J70" s="33"/>
+      <c r="K70" s="33"/>
+      <c r="L70" s="33"/>
+      <c r="M70" s="33"/>
+      <c r="N70" s="33"/>
+      <c r="O70" s="32">
         <v>9.7</v>
       </c>
-      <c r="P70" s="32"/>
-      <c r="Q70" s="32"/>
-      <c r="R70" s="32"/>
-      <c r="S70" s="31">
+      <c r="P70" s="33"/>
+      <c r="Q70" s="33"/>
+      <c r="R70" s="33"/>
+      <c r="S70" s="32">
         <v>41.77</v>
       </c>
-      <c r="T70" s="32"/>
-      <c r="U70" s="32"/>
-      <c r="V70" s="32"/>
-      <c r="W70" s="31">
+      <c r="T70" s="33"/>
+      <c r="U70" s="33"/>
+      <c r="V70" s="33"/>
+      <c r="W70" s="32">
         <v>7.25</v>
       </c>
-      <c r="X70" s="32"/>
-      <c r="Y70" s="32"/>
-      <c r="Z70" s="31">
+      <c r="X70" s="33"/>
+      <c r="Y70" s="33"/>
+      <c r="Z70" s="32">
         <v>14.09</v>
       </c>
-      <c r="AA70" s="31">
+      <c r="AA70" s="32">
         <v>6.61</v>
       </c>
-      <c r="AB70" s="32"/>
+      <c r="AB70" s="33"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="28" t="s">
-        <v>483</v>
-      </c>
-      <c r="B71" s="31">
+      <c r="A71" s="29" t="s">
+        <v>484</v>
+      </c>
+      <c r="B71" s="32">
         <v>16.45</v>
       </c>
-      <c r="C71" s="31">
+      <c r="C71" s="32">
         <v>17.38</v>
       </c>
-      <c r="D71" s="31">
+      <c r="D71" s="32">
         <v>9.86</v>
       </c>
-      <c r="E71" s="31">
+      <c r="E71" s="32">
         <v>8.62</v>
       </c>
-      <c r="F71" s="31">
+      <c r="F71" s="32">
         <v>9.61</v>
       </c>
-      <c r="G71" s="32"/>
-      <c r="H71" s="32"/>
-      <c r="I71" s="32"/>
-      <c r="J71" s="32"/>
-      <c r="K71" s="32"/>
-      <c r="L71" s="32"/>
-      <c r="M71" s="32"/>
-      <c r="N71" s="32"/>
-      <c r="O71" s="32"/>
-      <c r="P71" s="32"/>
-      <c r="Q71" s="32"/>
-      <c r="R71" s="32"/>
-      <c r="S71" s="32"/>
-      <c r="T71" s="32"/>
-      <c r="U71" s="32"/>
-      <c r="V71" s="32"/>
-      <c r="W71" s="32"/>
-      <c r="X71" s="32"/>
-      <c r="Y71" s="32"/>
-      <c r="Z71" s="32"/>
-      <c r="AA71" s="32"/>
-      <c r="AB71" s="32"/>
+      <c r="G71" s="33"/>
+      <c r="H71" s="33"/>
+      <c r="I71" s="33"/>
+      <c r="J71" s="33"/>
+      <c r="K71" s="33"/>
+      <c r="L71" s="33"/>
+      <c r="M71" s="33"/>
+      <c r="N71" s="33"/>
+      <c r="O71" s="33"/>
+      <c r="P71" s="33"/>
+      <c r="Q71" s="33"/>
+      <c r="R71" s="33"/>
+      <c r="S71" s="33"/>
+      <c r="T71" s="33"/>
+      <c r="U71" s="33"/>
+      <c r="V71" s="33"/>
+      <c r="W71" s="33"/>
+      <c r="X71" s="33"/>
+      <c r="Y71" s="33"/>
+      <c r="Z71" s="33"/>
+      <c r="AA71" s="33"/>
+      <c r="AB71" s="33"/>
     </row>
     <row r="72" ht="15.75" customHeight="1"/>
     <row r="73" ht="15.75" customHeight="1"/>
